--- a/excel_templates/Invoices_Report.xlsx
+++ b/excel_templates/Invoices_Report.xlsx
@@ -659,7 +659,7 @@
     <row r="1" ht="25.05" customHeight="1" thickBot="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>بيان الفواتير الغير مرحلة للفترة من 2025-03-28 وحتى 2025-04-03</t>
+          <t>بيان الفواتير النقدية للفترة من 2025-12-01 وحتى 2026-06-27</t>
         </is>
       </c>
       <c r="B1" s="18" t="n"/>
@@ -702,10 +702,10 @@
     </row>
     <row r="3" ht="60" customHeight="1" thickBot="1">
       <c r="A3" s="2" t="n">
-        <v>1</v>
+        <v>3870</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>45506</v>
+        <v>45992</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -714,1835 +714,5867 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Ayman Mahmoud</t>
+          <t>نادي السيارات الملكي</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
-        <v>960</v>
+        <v>60</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>KIA, Alto, Alto</t>
+          <t>4569</t>
         </is>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1" thickBot="1">
       <c r="A4" s="2" t="n">
-        <v>2</v>
+        <v>3880</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>45522</v>
+        <v>45992</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>ذمم</t>
+          <t>نقدي</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Ali Ahmed</t>
+          <t>احمد جلال</t>
         </is>
       </c>
       <c r="E4" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>48-61181</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1" thickBot="1">
+      <c r="A5" s="2" t="n">
+        <v>3906</v>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>45994</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>عدي البلبيسي</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>46-16502</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1" thickBot="1">
+      <c r="A6" s="2" t="n">
+        <v>3920</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>45997</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>نوير النبر</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>46-8283</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1" thickBot="1">
+      <c r="A7" s="2" t="n">
+        <v>3975</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>46001</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>باسل ابو محفوظ</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>22-18743</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1" thickBot="1">
+      <c r="A8" s="2" t="n">
+        <v>3987</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>46001</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>عمرو</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>46-57336</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1" thickBot="1">
+      <c r="A9" s="2" t="n">
+        <v>4022</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>46005</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>كميل نادر</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>46-10739</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1" thickBot="1">
+      <c r="A10" s="2" t="n">
+        <v>4034</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>46006</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>طارق البيطار</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>12-1596</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1" thickBot="1">
+      <c r="A11" s="2" t="n">
+        <v>4035</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>46006</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>حسن منصور</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>46-14560</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1" thickBot="1">
+      <c r="A12" s="2" t="n">
+        <v>4036</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>46006</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>يوسف زهران</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>36-61454</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1" thickBot="1">
+      <c r="A13" s="2" t="n">
+        <v>4044</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>46007</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>رامي ذيب</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>ور ٢٧٠</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1" thickBot="1">
+      <c r="A14" s="2" t="n">
+        <v>4052</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>د. احمد العبيسي</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>30-71060</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1" thickBot="1">
+      <c r="A15" s="2" t="n">
+        <v>4057</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>خالد الهواري</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>47-83440</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1" thickBot="1">
+      <c r="A16" s="2" t="n">
+        <v>4060</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>نادي السيارات الملكي</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1" thickBot="1">
+      <c r="A17" s="2" t="n">
+        <v>4061</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>نادي السيارات الملكي</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>456</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1" thickBot="1">
+      <c r="A18" s="2" t="n">
+        <v>4064</v>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>الدكتور عامر شعبان</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>MBJYMLA28TT132377 , JTMRW3FV7SD606093</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1" thickBot="1">
+      <c r="A19" s="2" t="n">
+        <v>4068</v>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>زياد اسبسيوتي</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>46-10431</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1" thickBot="1">
+      <c r="A20" s="2" t="n">
+        <v>4073</v>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>46010</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>علاء مخامرة</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>46-11645</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1" thickBot="1">
+      <c r="A21" s="2" t="n">
+        <v>4074</v>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>46010</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>ثائر محمد</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>17-63712</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1" thickBot="1">
+      <c r="A22" s="2" t="n">
+        <v>4076</v>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>46011</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>رمزي خربط</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>37-92280 , 46-88679</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1" thickBot="1">
+      <c r="A23" s="2" t="n">
+        <v>4085</v>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>46011</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>احمد الشعبي</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>46-13422</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1" thickBot="1">
+      <c r="A24" s="2" t="n">
+        <v>4087</v>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>46012</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>سمير السامرائي</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>45-39121</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1" thickBot="1">
+      <c r="A25" s="2" t="n">
+        <v>4091</v>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>46012</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>مريد مرار</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>46-3195</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1" thickBot="1">
+      <c r="A26" s="2" t="n">
+        <v>4102</v>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>46013</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>د. محمد سامي المحتسب</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>46-12164</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1" thickBot="1">
+      <c r="A27" s="2" t="n">
+        <v>4109</v>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>46013</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>احمد الشعبي</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>46-13422</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1" thickBot="1">
+      <c r="A28" s="2" t="n">
+        <v>4110</v>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>46014</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>مشعل البحري</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>46-12256</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1" thickBot="1">
+      <c r="A29" s="2" t="n">
+        <v>4116</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>46014</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>خالد وحيد</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>، 46-14874</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1" thickBot="1">
+      <c r="A30" s="2" t="n">
+        <v>4117</v>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>46014</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>عمر برجوس</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>46-92981</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="60" customHeight="1" thickBot="1">
+      <c r="A31" s="2" t="n">
+        <v>4119</v>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>46014</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>سيف بشير</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>45-60180</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="60" customHeight="1" thickBot="1">
+      <c r="A32" s="2" t="n">
+        <v>4135</v>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>46015</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>عدنان النواجي</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>36-90646</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1" thickBot="1">
+      <c r="A33" s="2" t="n">
+        <v>4142</v>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>46018</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>د. احمد بواعنة</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>46-12557</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1" thickBot="1">
+      <c r="A34" s="2" t="n">
+        <v>4150</v>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>46019</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>صلاح الشرايري</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>46-13899</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1" thickBot="1">
+      <c r="A35" s="2" t="n">
+        <v>4153</v>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>46019</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>ضياء الصرايرة</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>46-15227</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1" thickBot="1">
+      <c r="A36" s="2" t="n">
+        <v>4157</v>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>46019</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>نادي السيارات الملكي</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="60" customHeight="1" thickBot="1">
+      <c r="A37" s="2" t="n">
+        <v>4158</v>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>46019</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>نادي السيارات الملكي</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>1254</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="60" customHeight="1" thickBot="1">
+      <c r="A38" s="2" t="n">
+        <v>4168</v>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>46020</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>د. احمد بواعنة</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>46-12557</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="60" customHeight="1" thickBot="1">
+      <c r="A39" s="2" t="n">
+        <v>4202</v>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>46024</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>احمد علي</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>46-14127</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1" thickBot="1">
+      <c r="A40" s="2" t="n">
+        <v>4203</v>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>46024</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>حمزة الفايز</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="60" customHeight="1" thickBot="1">
+      <c r="A41" s="2" t="n">
+        <v>4221</v>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>46027</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>نور الكايد</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>46-14503</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="60" customHeight="1" thickBot="1">
+      <c r="A42" s="2" t="n">
+        <v>4228</v>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>46027</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>فيصل ابو طالب</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>46-7545</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="60" customHeight="1" thickBot="1">
+      <c r="A43" s="2" t="n">
+        <v>4232</v>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>46027</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>خالد الصرايرة</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>4060781</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="60" customHeight="1" thickBot="1">
+      <c r="A44" s="2" t="n">
+        <v>4242</v>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>سهل مرجي</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>46-11276</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="60" customHeight="1" thickBot="1">
+      <c r="A45" s="2" t="n">
+        <v>4245</v>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>غسان خوري</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>46-15033</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="60" customHeight="1" thickBot="1">
+      <c r="A46" s="2" t="n">
+        <v>4249</v>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>46029</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>زياد حلاق</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>46-12268</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="60" customHeight="1" thickBot="1">
+      <c r="A47" s="2" t="n">
+        <v>4250</v>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>46029</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>حمزة الفايز</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="60" customHeight="1" thickBot="1">
+      <c r="A48" s="2" t="n">
+        <v>4262</v>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>46030</v>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>بلال شكوكاني</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>46-10151</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="60" customHeight="1" thickBot="1">
+      <c r="A49" s="2" t="n">
+        <v>4265</v>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>46030</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>شركة الموجب لتجارة المركبات</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>66-95712</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="60" customHeight="1" thickBot="1">
+      <c r="A50" s="2" t="n">
+        <v>4267</v>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>46030</v>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>سهل مرجي</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>46-11276</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="60" customHeight="1" thickBot="1">
+      <c r="A51" s="2" t="n">
+        <v>4271</v>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>46030</v>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>رمزي خربط</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>37-92280 , 46-88679</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="60" customHeight="1" thickBot="1">
+      <c r="A52" s="2" t="n">
+        <v>4273</v>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>46030</v>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>محمد ابو النجا</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>١١</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="60" customHeight="1" thickBot="1">
+      <c r="A53" s="2" t="n">
+        <v>4274</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>46030</v>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>فيصل ابو دقة</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>46-43742</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="60" customHeight="1" thickBot="1">
+      <c r="A54" s="2" t="n">
+        <v>4291</v>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>46033</v>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>عمار بلقر</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>11-4109</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="60" customHeight="1" thickBot="1">
+      <c r="A55" s="2" t="n">
+        <v>4303</v>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>46034</v>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>عامر الطراونة</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>46-9837</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="60" customHeight="1" thickBot="1">
+      <c r="A56" s="2" t="n">
+        <v>4306</v>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>46034</v>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>حسن وهداني</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>48-85568</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="60" customHeight="1" thickBot="1">
+      <c r="A57" s="2" t="n">
+        <v>4310</v>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>46034</v>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>ابراهيم الشويات</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>40-94988</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="60" customHeight="1" thickBot="1">
+      <c r="A58" s="2" t="n">
+        <v>4312</v>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>46034</v>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>حمزة الفايز</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="60" customHeight="1" thickBot="1">
+      <c r="A59" s="2" t="n">
+        <v>4315</v>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>46034</v>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>احمد جلال</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>48-61811</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="60" customHeight="1" thickBot="1">
+      <c r="A60" s="2" t="n">
+        <v>4333</v>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>46036</v>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>ايمن سلطان</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>46-13735</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="60" customHeight="1" thickBot="1">
+      <c r="A61" s="2" t="n">
+        <v>4334</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>46036</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>رمزي خربط</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>37-92280</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="60" customHeight="1" thickBot="1">
+      <c r="A62" s="2" t="n">
+        <v>4338</v>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>46036</v>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>نادي السيارات الملكي</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>11221</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="60" customHeight="1" thickBot="1">
+      <c r="A63" s="2" t="n">
+        <v>4339</v>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>46036</v>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>نادي السيارات الملكي</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>2222</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="60" customHeight="1" thickBot="1">
+      <c r="A64" s="2" t="n">
+        <v>4345</v>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>46037</v>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>حمزة الجابري</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>45-71423</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="60" customHeight="1" thickBot="1">
+      <c r="A65" s="2" t="n">
+        <v>4348</v>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>46037</v>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>أنس رشيد</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>44-44998</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="60" customHeight="1" thickBot="1">
+      <c r="A66" s="2" t="n">
+        <v>4358</v>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>46038</v>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>عبدالله الشركسي</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>37-59763</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="60" customHeight="1" thickBot="1">
+      <c r="A67" s="2" t="n">
+        <v>4359</v>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>46039</v>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>فيصل ابو دقة</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>46-43742</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="60" customHeight="1" thickBot="1">
+      <c r="A68" s="2" t="n">
+        <v>4361</v>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>46039</v>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>الشركة المثالية للمزادات الالكترونية</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>46-51750</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="60" customHeight="1" thickBot="1">
+      <c r="A69" s="2" t="n">
+        <v>4374</v>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>46040</v>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>شركة مسار</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="60" customHeight="1" thickBot="1">
+      <c r="A70" s="2" t="n">
+        <v>4386</v>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>46041</v>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>مصطفى جلنبو</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>Suzuki</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="7" t="n"/>
-    </row>
-    <row r="6" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="7" t="n"/>
-    </row>
-    <row r="7" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A7" s="2" t="n"/>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="7" t="n"/>
-    </row>
-    <row r="8" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A8" s="2" t="n"/>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="7" t="n"/>
-    </row>
-    <row r="9" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A9" s="2" t="n"/>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="7" t="n"/>
-    </row>
-    <row r="10" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A10" s="2" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="7" t="n"/>
-    </row>
-    <row r="11" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A11" s="2" t="n"/>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="7" t="n"/>
-    </row>
-    <row r="12" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A12" s="2" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="7" t="n"/>
-    </row>
-    <row r="13" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A13" s="2" t="n"/>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="7" t="n"/>
-    </row>
-    <row r="14" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A14" s="2" t="n"/>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="7" t="n"/>
-    </row>
-    <row r="15" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A15" s="2" t="n"/>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="7" t="n"/>
-    </row>
-    <row r="16" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A16" s="2" t="n"/>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="7" t="n"/>
-    </row>
-    <row r="17" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A17" s="2" t="n"/>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="7" t="n"/>
-    </row>
-    <row r="18" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A18" s="2" t="n"/>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="7" t="n"/>
-    </row>
-    <row r="19" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="7" t="n"/>
-    </row>
-    <row r="20" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="7" t="n"/>
-    </row>
-    <row r="21" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A21" s="2" t="n"/>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="7" t="n"/>
-    </row>
-    <row r="22" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A22" s="2" t="n"/>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="7" t="n"/>
-    </row>
-    <row r="23" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A23" s="2" t="n"/>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="7" t="n"/>
-    </row>
-    <row r="24" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A24" s="2" t="n"/>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="7" t="n"/>
-    </row>
-    <row r="25" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A25" s="2" t="n"/>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="7" t="n"/>
-    </row>
-    <row r="26" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A26" s="2" t="n"/>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="7" t="n"/>
-    </row>
-    <row r="27" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A27" s="2" t="n"/>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="7" t="n"/>
-    </row>
-    <row r="28" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A28" s="2" t="n"/>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n"/>
-      <c r="E28" s="6" t="n"/>
-      <c r="F28" s="7" t="n"/>
-    </row>
-    <row r="29" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A29" s="2" t="n"/>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="7" t="n"/>
-    </row>
-    <row r="30" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A30" s="2" t="n"/>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="6" t="n"/>
-      <c r="F30" s="7" t="n"/>
-    </row>
-    <row r="31" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="6" t="n"/>
-      <c r="F31" s="7" t="n"/>
-    </row>
-    <row r="32" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A32" s="2" t="n"/>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="7" t="n"/>
-    </row>
-    <row r="33" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A33" s="2" t="n"/>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n"/>
-      <c r="E33" s="6" t="n"/>
-      <c r="F33" s="7" t="n"/>
-    </row>
-    <row r="34" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A34" s="2" t="n"/>
-      <c r="B34" s="5" t="n"/>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" s="6" t="n"/>
-      <c r="F34" s="7" t="n"/>
-    </row>
-    <row r="35" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A35" s="2" t="n"/>
-      <c r="B35" s="5" t="n"/>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="n"/>
-      <c r="E35" s="6" t="n"/>
-      <c r="F35" s="7" t="n"/>
-    </row>
-    <row r="36" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A36" s="2" t="n"/>
-      <c r="B36" s="5" t="n"/>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n"/>
-      <c r="E36" s="6" t="n"/>
-      <c r="F36" s="7" t="n"/>
-    </row>
-    <row r="37" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A37" s="2" t="n"/>
-      <c r="B37" s="5" t="n"/>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="6" t="n"/>
-      <c r="F37" s="7" t="n"/>
-    </row>
-    <row r="38" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A38" s="2" t="n"/>
-      <c r="B38" s="5" t="n"/>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n"/>
-      <c r="E38" s="6" t="n"/>
-      <c r="F38" s="7" t="n"/>
-    </row>
-    <row r="39" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A39" s="2" t="n"/>
-      <c r="B39" s="5" t="n"/>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n"/>
-      <c r="E39" s="6" t="n"/>
-      <c r="F39" s="7" t="n"/>
-    </row>
-    <row r="40" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A40" s="2" t="n"/>
-      <c r="B40" s="5" t="n"/>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n"/>
-      <c r="E40" s="6" t="n"/>
-      <c r="F40" s="7" t="n"/>
-    </row>
-    <row r="41" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="5" t="n"/>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n"/>
-      <c r="E41" s="6" t="n"/>
-      <c r="F41" s="7" t="n"/>
-    </row>
-    <row r="42" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A42" s="2" t="n"/>
-      <c r="B42" s="5" t="n"/>
-      <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="n"/>
-      <c r="E42" s="6" t="n"/>
-      <c r="F42" s="7" t="n"/>
-    </row>
-    <row r="43" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A43" s="2" t="n"/>
-      <c r="B43" s="5" t="n"/>
-      <c r="C43" s="2" t="n"/>
-      <c r="D43" s="2" t="n"/>
-      <c r="E43" s="6" t="n"/>
-      <c r="F43" s="7" t="n"/>
-    </row>
-    <row r="44" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A44" s="2" t="n"/>
-      <c r="B44" s="5" t="n"/>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n"/>
-      <c r="E44" s="6" t="n"/>
-      <c r="F44" s="7" t="n"/>
-    </row>
-    <row r="45" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A45" s="2" t="n"/>
-      <c r="B45" s="5" t="n"/>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n"/>
-      <c r="E45" s="6" t="n"/>
-      <c r="F45" s="7" t="n"/>
-    </row>
-    <row r="46" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A46" s="2" t="n"/>
-      <c r="B46" s="5" t="n"/>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n"/>
-      <c r="E46" s="6" t="n"/>
-      <c r="F46" s="7" t="n"/>
-    </row>
-    <row r="47" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A47" s="2" t="n"/>
-      <c r="B47" s="5" t="n"/>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n"/>
-      <c r="E47" s="6" t="n"/>
-      <c r="F47" s="7" t="n"/>
-    </row>
-    <row r="48" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A48" s="2" t="n"/>
-      <c r="B48" s="5" t="n"/>
-      <c r="C48" s="2" t="n"/>
-      <c r="D48" s="2" t="n"/>
-      <c r="E48" s="6" t="n"/>
-      <c r="F48" s="7" t="n"/>
-    </row>
-    <row r="49" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A49" s="2" t="n"/>
-      <c r="B49" s="5" t="n"/>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n"/>
-      <c r="E49" s="6" t="n"/>
-      <c r="F49" s="7" t="n"/>
-    </row>
-    <row r="50" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A50" s="2" t="n"/>
-      <c r="B50" s="5" t="n"/>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n"/>
-      <c r="E50" s="6" t="n"/>
-      <c r="F50" s="7" t="n"/>
-    </row>
-    <row r="51" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A51" s="2" t="n"/>
-      <c r="B51" s="5" t="n"/>
-      <c r="C51" s="2" t="n"/>
-      <c r="D51" s="2" t="n"/>
-      <c r="E51" s="6" t="n"/>
-      <c r="F51" s="7" t="n"/>
-    </row>
-    <row r="52" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A52" s="2" t="n"/>
-      <c r="B52" s="5" t="n"/>
-      <c r="C52" s="2" t="n"/>
-      <c r="D52" s="2" t="n"/>
-      <c r="E52" s="6" t="n"/>
-      <c r="F52" s="7" t="n"/>
-    </row>
-    <row r="53" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A53" s="2" t="n"/>
-      <c r="B53" s="5" t="n"/>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="n"/>
-      <c r="E53" s="6" t="n"/>
-      <c r="F53" s="7" t="n"/>
-    </row>
-    <row r="54" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A54" s="2" t="n"/>
-      <c r="B54" s="5" t="n"/>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n"/>
-      <c r="E54" s="6" t="n"/>
-      <c r="F54" s="7" t="n"/>
-    </row>
-    <row r="55" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A55" s="2" t="n"/>
-      <c r="B55" s="5" t="n"/>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="n"/>
-      <c r="E55" s="6" t="n"/>
-      <c r="F55" s="7" t="n"/>
-    </row>
-    <row r="56" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A56" s="2" t="n"/>
-      <c r="B56" s="5" t="n"/>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="n"/>
-      <c r="E56" s="6" t="n"/>
-      <c r="F56" s="7" t="n"/>
-    </row>
-    <row r="57" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A57" s="2" t="n"/>
-      <c r="B57" s="5" t="n"/>
-      <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="n"/>
-      <c r="E57" s="6" t="n"/>
-      <c r="F57" s="7" t="n"/>
-    </row>
-    <row r="58" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A58" s="2" t="n"/>
-      <c r="B58" s="5" t="n"/>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n"/>
-      <c r="E58" s="6" t="n"/>
-      <c r="F58" s="7" t="n"/>
-    </row>
-    <row r="59" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A59" s="2" t="n"/>
-      <c r="B59" s="5" t="n"/>
-      <c r="C59" s="2" t="n"/>
-      <c r="D59" s="2" t="n"/>
-      <c r="E59" s="6" t="n"/>
-      <c r="F59" s="7" t="n"/>
-    </row>
-    <row r="60" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A60" s="2" t="n"/>
-      <c r="B60" s="5" t="n"/>
-      <c r="C60" s="2" t="n"/>
-      <c r="D60" s="2" t="n"/>
-      <c r="E60" s="6" t="n"/>
-      <c r="F60" s="7" t="n"/>
-    </row>
-    <row r="61" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A61" s="2" t="n"/>
-      <c r="B61" s="5" t="n"/>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="n"/>
-      <c r="E61" s="6" t="n"/>
-      <c r="F61" s="7" t="n"/>
-    </row>
-    <row r="62" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A62" s="2" t="n"/>
-      <c r="B62" s="5" t="n"/>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="n"/>
-      <c r="E62" s="6" t="n"/>
-      <c r="F62" s="7" t="n"/>
-    </row>
-    <row r="63" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A63" s="2" t="n"/>
-      <c r="B63" s="5" t="n"/>
-      <c r="C63" s="2" t="n"/>
-      <c r="D63" s="2" t="n"/>
-      <c r="E63" s="6" t="n"/>
-      <c r="F63" s="7" t="n"/>
-    </row>
-    <row r="64" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A64" s="2" t="n"/>
-      <c r="B64" s="5" t="n"/>
-      <c r="C64" s="2" t="n"/>
-      <c r="D64" s="2" t="n"/>
-      <c r="E64" s="6" t="n"/>
-      <c r="F64" s="7" t="n"/>
-    </row>
-    <row r="65" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A65" s="2" t="n"/>
-      <c r="B65" s="5" t="n"/>
-      <c r="C65" s="2" t="n"/>
-      <c r="D65" s="2" t="n"/>
-      <c r="E65" s="6" t="n"/>
-      <c r="F65" s="7" t="n"/>
-    </row>
-    <row r="66" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A66" s="2" t="n"/>
-      <c r="B66" s="5" t="n"/>
-      <c r="C66" s="2" t="n"/>
-      <c r="D66" s="2" t="n"/>
-      <c r="E66" s="6" t="n"/>
-      <c r="F66" s="7" t="n"/>
-    </row>
-    <row r="67" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A67" s="2" t="n"/>
-      <c r="B67" s="5" t="n"/>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n"/>
-      <c r="E67" s="6" t="n"/>
-      <c r="F67" s="7" t="n"/>
-    </row>
-    <row r="68" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A68" s="2" t="n"/>
-      <c r="B68" s="5" t="n"/>
-      <c r="C68" s="2" t="n"/>
-      <c r="D68" s="2" t="n"/>
-      <c r="E68" s="6" t="n"/>
-      <c r="F68" s="7" t="n"/>
-    </row>
-    <row r="69" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A69" s="2" t="n"/>
-      <c r="B69" s="5" t="n"/>
-      <c r="C69" s="2" t="n"/>
-      <c r="D69" s="2" t="n"/>
-      <c r="E69" s="6" t="n"/>
-      <c r="F69" s="7" t="n"/>
-    </row>
-    <row r="70" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A70" s="2" t="n"/>
-      <c r="B70" s="5" t="n"/>
-      <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="n"/>
-      <c r="E70" s="6" t="n"/>
-      <c r="F70" s="7" t="n"/>
-    </row>
-    <row r="71" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A71" s="2" t="n"/>
-      <c r="B71" s="5" t="n"/>
-      <c r="C71" s="2" t="n"/>
-      <c r="D71" s="2" t="n"/>
-      <c r="E71" s="6" t="n"/>
-      <c r="F71" s="7" t="n"/>
-    </row>
-    <row r="72" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A72" s="2" t="n"/>
-      <c r="B72" s="5" t="n"/>
-      <c r="C72" s="2" t="n"/>
-      <c r="D72" s="2" t="n"/>
-      <c r="E72" s="6" t="n"/>
-      <c r="F72" s="7" t="n"/>
-    </row>
-    <row r="73" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A73" s="2" t="n"/>
-      <c r="B73" s="5" t="n"/>
-      <c r="C73" s="2" t="n"/>
-      <c r="D73" s="2" t="n"/>
-      <c r="E73" s="6" t="n"/>
-      <c r="F73" s="7" t="n"/>
-    </row>
-    <row r="74" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A74" s="2" t="n"/>
-      <c r="B74" s="5" t="n"/>
-      <c r="C74" s="2" t="n"/>
-      <c r="D74" s="2" t="n"/>
-      <c r="E74" s="6" t="n"/>
-      <c r="F74" s="7" t="n"/>
-    </row>
-    <row r="75" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A75" s="2" t="n"/>
-      <c r="B75" s="5" t="n"/>
-      <c r="C75" s="2" t="n"/>
-      <c r="D75" s="2" t="n"/>
-      <c r="E75" s="6" t="n"/>
-      <c r="F75" s="7" t="n"/>
-    </row>
-    <row r="76" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A76" s="2" t="n"/>
-      <c r="B76" s="5" t="n"/>
-      <c r="C76" s="2" t="n"/>
-      <c r="D76" s="2" t="n"/>
-      <c r="E76" s="6" t="n"/>
-      <c r="F76" s="7" t="n"/>
-    </row>
-    <row r="77" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A77" s="2" t="n"/>
-      <c r="B77" s="5" t="n"/>
-      <c r="C77" s="2" t="n"/>
-      <c r="D77" s="2" t="n"/>
-      <c r="E77" s="6" t="n"/>
-      <c r="F77" s="7" t="n"/>
-    </row>
-    <row r="78" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A78" s="2" t="n"/>
-      <c r="B78" s="5" t="n"/>
-      <c r="C78" s="2" t="n"/>
-      <c r="D78" s="2" t="n"/>
-      <c r="E78" s="6" t="n"/>
-      <c r="F78" s="7" t="n"/>
-    </row>
-    <row r="79" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A79" s="2" t="n"/>
-      <c r="B79" s="5" t="n"/>
-      <c r="C79" s="2" t="n"/>
-      <c r="D79" s="2" t="n"/>
-      <c r="E79" s="6" t="n"/>
-      <c r="F79" s="7" t="n"/>
-    </row>
-    <row r="80" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A80" s="2" t="n"/>
-      <c r="B80" s="5" t="n"/>
-      <c r="C80" s="2" t="n"/>
-      <c r="D80" s="2" t="n"/>
-      <c r="E80" s="6" t="n"/>
-      <c r="F80" s="7" t="n"/>
-    </row>
-    <row r="81" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A81" s="2" t="n"/>
-      <c r="B81" s="5" t="n"/>
-      <c r="C81" s="2" t="n"/>
-      <c r="D81" s="2" t="n"/>
-      <c r="E81" s="6" t="n"/>
-      <c r="F81" s="7" t="n"/>
-    </row>
-    <row r="82" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A82" s="2" t="n"/>
-      <c r="B82" s="5" t="n"/>
-      <c r="C82" s="2" t="n"/>
-      <c r="D82" s="2" t="n"/>
-      <c r="E82" s="6" t="n"/>
-      <c r="F82" s="7" t="n"/>
-    </row>
-    <row r="83" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A83" s="2" t="n"/>
-      <c r="B83" s="5" t="n"/>
-      <c r="C83" s="2" t="n"/>
-      <c r="D83" s="2" t="n"/>
-      <c r="E83" s="6" t="n"/>
-      <c r="F83" s="7" t="n"/>
-    </row>
-    <row r="84" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A84" s="2" t="n"/>
-      <c r="B84" s="5" t="n"/>
-      <c r="C84" s="2" t="n"/>
-      <c r="D84" s="2" t="n"/>
-      <c r="E84" s="6" t="n"/>
-      <c r="F84" s="7" t="n"/>
-    </row>
-    <row r="85" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A85" s="2" t="n"/>
-      <c r="B85" s="5" t="n"/>
-      <c r="C85" s="2" t="n"/>
-      <c r="D85" s="2" t="n"/>
-      <c r="E85" s="6" t="n"/>
-      <c r="F85" s="7" t="n"/>
-    </row>
-    <row r="86" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A86" s="2" t="n"/>
-      <c r="B86" s="5" t="n"/>
-      <c r="C86" s="2" t="n"/>
-      <c r="D86" s="2" t="n"/>
-      <c r="E86" s="6" t="n"/>
-      <c r="F86" s="7" t="n"/>
-    </row>
-    <row r="87" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A87" s="2" t="n"/>
-      <c r="B87" s="5" t="n"/>
-      <c r="C87" s="2" t="n"/>
-      <c r="D87" s="2" t="n"/>
-      <c r="E87" s="6" t="n"/>
-      <c r="F87" s="7" t="n"/>
-    </row>
-    <row r="88" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A88" s="2" t="n"/>
-      <c r="B88" s="5" t="n"/>
-      <c r="C88" s="2" t="n"/>
-      <c r="D88" s="2" t="n"/>
-      <c r="E88" s="6" t="n"/>
-      <c r="F88" s="7" t="n"/>
-    </row>
-    <row r="89" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A89" s="2" t="n"/>
-      <c r="B89" s="5" t="n"/>
-      <c r="C89" s="2" t="n"/>
-      <c r="D89" s="2" t="n"/>
-      <c r="E89" s="6" t="n"/>
-      <c r="F89" s="7" t="n"/>
-    </row>
-    <row r="90" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A90" s="2" t="n"/>
-      <c r="B90" s="5" t="n"/>
-      <c r="C90" s="2" t="n"/>
-      <c r="D90" s="2" t="n"/>
-      <c r="E90" s="6" t="n"/>
-      <c r="F90" s="7" t="n"/>
-    </row>
-    <row r="91" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A91" s="2" t="n"/>
-      <c r="B91" s="5" t="n"/>
-      <c r="C91" s="2" t="n"/>
-      <c r="D91" s="2" t="n"/>
-      <c r="E91" s="6" t="n"/>
-      <c r="F91" s="7" t="n"/>
-    </row>
-    <row r="92" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A92" s="2" t="n"/>
-      <c r="B92" s="5" t="n"/>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n"/>
-      <c r="E92" s="6" t="n"/>
-      <c r="F92" s="7" t="n"/>
-    </row>
-    <row r="93" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A93" s="2" t="n"/>
-      <c r="B93" s="5" t="n"/>
-      <c r="C93" s="2" t="n"/>
-      <c r="D93" s="2" t="n"/>
-      <c r="E93" s="6" t="n"/>
-      <c r="F93" s="7" t="n"/>
-    </row>
-    <row r="94" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A94" s="2" t="n"/>
-      <c r="B94" s="5" t="n"/>
-      <c r="C94" s="2" t="n"/>
-      <c r="D94" s="2" t="n"/>
-      <c r="E94" s="6" t="n"/>
-      <c r="F94" s="7" t="n"/>
-    </row>
-    <row r="95" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A95" s="2" t="n"/>
-      <c r="B95" s="5" t="n"/>
-      <c r="C95" s="2" t="n"/>
-      <c r="D95" s="2" t="n"/>
-      <c r="E95" s="6" t="n"/>
-      <c r="F95" s="7" t="n"/>
-    </row>
-    <row r="96" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A96" s="2" t="n"/>
-      <c r="B96" s="5" t="n"/>
-      <c r="C96" s="2" t="n"/>
-      <c r="D96" s="2" t="n"/>
-      <c r="E96" s="6" t="n"/>
-      <c r="F96" s="7" t="n"/>
-    </row>
-    <row r="97" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A97" s="2" t="n"/>
-      <c r="B97" s="5" t="n"/>
-      <c r="C97" s="2" t="n"/>
-      <c r="D97" s="2" t="n"/>
-      <c r="E97" s="6" t="n"/>
-      <c r="F97" s="7" t="n"/>
-    </row>
-    <row r="98" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A98" s="2" t="n"/>
-      <c r="B98" s="5" t="n"/>
-      <c r="C98" s="2" t="n"/>
-      <c r="D98" s="2" t="n"/>
-      <c r="E98" s="6" t="n"/>
-      <c r="F98" s="7" t="n"/>
-    </row>
-    <row r="99" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A99" s="2" t="n"/>
-      <c r="B99" s="5" t="n"/>
-      <c r="C99" s="2" t="n"/>
-      <c r="D99" s="2" t="n"/>
-      <c r="E99" s="6" t="n"/>
-      <c r="F99" s="7" t="n"/>
-    </row>
-    <row r="100" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A100" s="2" t="n"/>
-      <c r="B100" s="5" t="n"/>
-      <c r="C100" s="2" t="n"/>
-      <c r="D100" s="2" t="n"/>
-      <c r="E100" s="6" t="n"/>
-      <c r="F100" s="7" t="n"/>
-    </row>
-    <row r="101" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A101" s="2" t="n"/>
-      <c r="B101" s="5" t="n"/>
-      <c r="C101" s="2" t="n"/>
-      <c r="D101" s="2" t="n"/>
-      <c r="E101" s="6" t="n"/>
-      <c r="F101" s="7" t="n"/>
-    </row>
-    <row r="102" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A102" s="2" t="n"/>
-      <c r="B102" s="5" t="n"/>
-      <c r="C102" s="2" t="n"/>
-      <c r="D102" s="2" t="n"/>
-      <c r="E102" s="6" t="n"/>
-      <c r="F102" s="7" t="n"/>
-    </row>
-    <row r="103" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A103" s="2" t="n"/>
-      <c r="B103" s="5" t="n"/>
-      <c r="C103" s="2" t="n"/>
-      <c r="D103" s="2" t="n"/>
-      <c r="E103" s="6" t="n"/>
-      <c r="F103" s="7" t="n"/>
-    </row>
-    <row r="104" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A104" s="2" t="n"/>
-      <c r="B104" s="5" t="n"/>
-      <c r="C104" s="2" t="n"/>
-      <c r="D104" s="2" t="n"/>
-      <c r="E104" s="6" t="n"/>
-      <c r="F104" s="7" t="n"/>
-    </row>
-    <row r="105" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A105" s="2" t="n"/>
-      <c r="B105" s="5" t="n"/>
-      <c r="C105" s="2" t="n"/>
-      <c r="D105" s="2" t="n"/>
-      <c r="E105" s="6" t="n"/>
-      <c r="F105" s="7" t="n"/>
-    </row>
-    <row r="106" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A106" s="2" t="n"/>
-      <c r="B106" s="5" t="n"/>
-      <c r="C106" s="2" t="n"/>
-      <c r="D106" s="2" t="n"/>
-      <c r="E106" s="6" t="n"/>
-      <c r="F106" s="7" t="n"/>
-    </row>
-    <row r="107" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A107" s="2" t="n"/>
-      <c r="B107" s="5" t="n"/>
-      <c r="C107" s="2" t="n"/>
-      <c r="D107" s="2" t="n"/>
-      <c r="E107" s="6" t="n"/>
-      <c r="F107" s="7" t="n"/>
-    </row>
-    <row r="108" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A108" s="2" t="n"/>
-      <c r="B108" s="5" t="n"/>
-      <c r="C108" s="2" t="n"/>
-      <c r="D108" s="2" t="n"/>
-      <c r="E108" s="6" t="n"/>
-      <c r="F108" s="7" t="n"/>
-    </row>
-    <row r="109" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A109" s="2" t="n"/>
-      <c r="B109" s="5" t="n"/>
-      <c r="C109" s="2" t="n"/>
-      <c r="D109" s="2" t="n"/>
-      <c r="E109" s="6" t="n"/>
-      <c r="F109" s="7" t="n"/>
-    </row>
-    <row r="110" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A110" s="2" t="n"/>
-      <c r="B110" s="5" t="n"/>
-      <c r="C110" s="2" t="n"/>
-      <c r="D110" s="2" t="n"/>
-      <c r="E110" s="6" t="n"/>
-      <c r="F110" s="7" t="n"/>
-    </row>
-    <row r="111" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A111" s="2" t="n"/>
-      <c r="B111" s="5" t="n"/>
-      <c r="C111" s="2" t="n"/>
-      <c r="D111" s="2" t="n"/>
-      <c r="E111" s="6" t="n"/>
-      <c r="F111" s="7" t="n"/>
-    </row>
-    <row r="112" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A112" s="2" t="n"/>
-      <c r="B112" s="5" t="n"/>
-      <c r="C112" s="2" t="n"/>
-      <c r="D112" s="2" t="n"/>
-      <c r="E112" s="6" t="n"/>
-      <c r="F112" s="7" t="n"/>
-    </row>
-    <row r="113" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A113" s="2" t="n"/>
-      <c r="B113" s="5" t="n"/>
-      <c r="C113" s="2" t="n"/>
-      <c r="D113" s="2" t="n"/>
-      <c r="E113" s="6" t="n"/>
-      <c r="F113" s="7" t="n"/>
-    </row>
-    <row r="114" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A114" s="2" t="n"/>
-      <c r="B114" s="5" t="n"/>
-      <c r="C114" s="2" t="n"/>
-      <c r="D114" s="2" t="n"/>
-      <c r="E114" s="6" t="n"/>
-      <c r="F114" s="7" t="n"/>
-    </row>
-    <row r="115" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A115" s="2" t="n"/>
-      <c r="B115" s="5" t="n"/>
-      <c r="C115" s="2" t="n"/>
-      <c r="D115" s="2" t="n"/>
-      <c r="E115" s="6" t="n"/>
-      <c r="F115" s="7" t="n"/>
-    </row>
-    <row r="116" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A116" s="2" t="n"/>
-      <c r="B116" s="5" t="n"/>
-      <c r="C116" s="2" t="n"/>
-      <c r="D116" s="2" t="n"/>
-      <c r="E116" s="6" t="n"/>
-      <c r="F116" s="7" t="n"/>
-    </row>
-    <row r="117" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A117" s="2" t="n"/>
-      <c r="B117" s="5" t="n"/>
-      <c r="C117" s="2" t="n"/>
-      <c r="D117" s="2" t="n"/>
-      <c r="E117" s="6" t="n"/>
-      <c r="F117" s="7" t="n"/>
-    </row>
-    <row r="118" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A118" s="2" t="n"/>
-      <c r="B118" s="5" t="n"/>
-      <c r="C118" s="2" t="n"/>
-      <c r="D118" s="2" t="n"/>
-      <c r="E118" s="6" t="n"/>
-      <c r="F118" s="7" t="n"/>
-    </row>
-    <row r="119" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A119" s="2" t="n"/>
-      <c r="B119" s="5" t="n"/>
-      <c r="C119" s="2" t="n"/>
-      <c r="D119" s="2" t="n"/>
-      <c r="E119" s="6" t="n"/>
-      <c r="F119" s="7" t="n"/>
-    </row>
-    <row r="120" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A120" s="2" t="n"/>
-      <c r="B120" s="5" t="n"/>
-      <c r="C120" s="2" t="n"/>
-      <c r="D120" s="2" t="n"/>
-      <c r="E120" s="6" t="n"/>
-      <c r="F120" s="7" t="n"/>
-    </row>
-    <row r="121" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A121" s="2" t="n"/>
-      <c r="B121" s="5" t="n"/>
-      <c r="C121" s="2" t="n"/>
-      <c r="D121" s="2" t="n"/>
-      <c r="E121" s="6" t="n"/>
-      <c r="F121" s="7" t="n"/>
-    </row>
-    <row r="122" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A122" s="2" t="n"/>
-      <c r="B122" s="5" t="n"/>
-      <c r="C122" s="2" t="n"/>
-      <c r="D122" s="2" t="n"/>
-      <c r="E122" s="6" t="n"/>
-      <c r="F122" s="7" t="n"/>
-    </row>
-    <row r="123" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A123" s="2" t="n"/>
-      <c r="B123" s="5" t="n"/>
-      <c r="C123" s="2" t="n"/>
-      <c r="D123" s="2" t="n"/>
-      <c r="E123" s="6" t="n"/>
-      <c r="F123" s="7" t="n"/>
-    </row>
-    <row r="124" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A124" s="2" t="n"/>
-      <c r="B124" s="5" t="n"/>
-      <c r="C124" s="2" t="n"/>
-      <c r="D124" s="2" t="n"/>
-      <c r="E124" s="6" t="n"/>
-      <c r="F124" s="7" t="n"/>
-    </row>
-    <row r="125" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A125" s="2" t="n"/>
-      <c r="B125" s="5" t="n"/>
-      <c r="C125" s="2" t="n"/>
-      <c r="D125" s="2" t="n"/>
-      <c r="E125" s="6" t="n"/>
-      <c r="F125" s="7" t="n"/>
-    </row>
-    <row r="126" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A126" s="2" t="n"/>
-      <c r="B126" s="5" t="n"/>
-      <c r="C126" s="2" t="n"/>
-      <c r="D126" s="2" t="n"/>
-      <c r="E126" s="6" t="n"/>
-      <c r="F126" s="7" t="n"/>
-    </row>
-    <row r="127" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A127" s="2" t="n"/>
-      <c r="B127" s="5" t="n"/>
-      <c r="C127" s="2" t="n"/>
-      <c r="D127" s="2" t="n"/>
-      <c r="E127" s="6" t="n"/>
-      <c r="F127" s="7" t="n"/>
-    </row>
-    <row r="128" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A128" s="2" t="n"/>
-      <c r="B128" s="5" t="n"/>
-      <c r="C128" s="2" t="n"/>
-      <c r="D128" s="2" t="n"/>
-      <c r="E128" s="6" t="n"/>
-      <c r="F128" s="7" t="n"/>
-    </row>
-    <row r="129" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A129" s="2" t="n"/>
-      <c r="B129" s="5" t="n"/>
-      <c r="C129" s="2" t="n"/>
-      <c r="D129" s="2" t="n"/>
-      <c r="E129" s="6" t="n"/>
-      <c r="F129" s="7" t="n"/>
-    </row>
-    <row r="130" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A130" s="2" t="n"/>
-      <c r="B130" s="5" t="n"/>
-      <c r="C130" s="2" t="n"/>
-      <c r="D130" s="2" t="n"/>
-      <c r="E130" s="6" t="n"/>
-      <c r="F130" s="7" t="n"/>
-    </row>
-    <row r="131" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A131" s="2" t="n"/>
-      <c r="B131" s="5" t="n"/>
-      <c r="C131" s="2" t="n"/>
-      <c r="D131" s="2" t="n"/>
-      <c r="E131" s="6" t="n"/>
-      <c r="F131" s="7" t="n"/>
-    </row>
-    <row r="132" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A132" s="2" t="n"/>
-      <c r="B132" s="5" t="n"/>
-      <c r="C132" s="2" t="n"/>
-      <c r="D132" s="2" t="n"/>
-      <c r="E132" s="6" t="n"/>
-      <c r="F132" s="7" t="n"/>
-    </row>
-    <row r="133" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A133" s="2" t="n"/>
-      <c r="B133" s="5" t="n"/>
-      <c r="C133" s="2" t="n"/>
-      <c r="D133" s="2" t="n"/>
-      <c r="E133" s="6" t="n"/>
-      <c r="F133" s="7" t="n"/>
-    </row>
-    <row r="134" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A134" s="2" t="n"/>
-      <c r="B134" s="5" t="n"/>
-      <c r="C134" s="2" t="n"/>
-      <c r="D134" s="2" t="n"/>
-      <c r="E134" s="6" t="n"/>
-      <c r="F134" s="7" t="n"/>
-    </row>
-    <row r="135" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A135" s="2" t="n"/>
-      <c r="B135" s="5" t="n"/>
-      <c r="C135" s="2" t="n"/>
-      <c r="D135" s="2" t="n"/>
-      <c r="E135" s="6" t="n"/>
-      <c r="F135" s="7" t="n"/>
-    </row>
-    <row r="136" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A136" s="2" t="n"/>
-      <c r="B136" s="5" t="n"/>
-      <c r="C136" s="2" t="n"/>
-      <c r="D136" s="2" t="n"/>
-      <c r="E136" s="6" t="n"/>
-      <c r="F136" s="7" t="n"/>
-    </row>
-    <row r="137" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A137" s="2" t="n"/>
-      <c r="B137" s="5" t="n"/>
-      <c r="C137" s="2" t="n"/>
-      <c r="D137" s="2" t="n"/>
-      <c r="E137" s="6" t="n"/>
-      <c r="F137" s="7" t="n"/>
-    </row>
-    <row r="138" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A138" s="2" t="n"/>
-      <c r="B138" s="5" t="n"/>
-      <c r="C138" s="2" t="n"/>
-      <c r="D138" s="2" t="n"/>
-      <c r="E138" s="6" t="n"/>
-      <c r="F138" s="7" t="n"/>
-    </row>
-    <row r="139" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A139" s="2" t="n"/>
-      <c r="B139" s="5" t="n"/>
-      <c r="C139" s="2" t="n"/>
-      <c r="D139" s="2" t="n"/>
-      <c r="E139" s="6" t="n"/>
-      <c r="F139" s="7" t="n"/>
-    </row>
-    <row r="140" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A140" s="2" t="n"/>
-      <c r="B140" s="5" t="n"/>
-      <c r="C140" s="2" t="n"/>
-      <c r="D140" s="2" t="n"/>
-      <c r="E140" s="6" t="n"/>
-      <c r="F140" s="7" t="n"/>
-    </row>
-    <row r="141" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A141" s="2" t="n"/>
-      <c r="B141" s="5" t="n"/>
-      <c r="C141" s="2" t="n"/>
-      <c r="D141" s="2" t="n"/>
-      <c r="E141" s="6" t="n"/>
-      <c r="F141" s="7" t="n"/>
-    </row>
-    <row r="142" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A142" s="2" t="n"/>
-      <c r="B142" s="5" t="n"/>
-      <c r="C142" s="2" t="n"/>
-      <c r="D142" s="2" t="n"/>
-      <c r="E142" s="6" t="n"/>
-      <c r="F142" s="7" t="n"/>
-    </row>
-    <row r="143" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A143" s="2" t="n"/>
-      <c r="B143" s="5" t="n"/>
-      <c r="C143" s="2" t="n"/>
-      <c r="D143" s="2" t="n"/>
-      <c r="E143" s="6" t="n"/>
-      <c r="F143" s="7" t="n"/>
-    </row>
-    <row r="144" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A144" s="2" t="n"/>
-      <c r="B144" s="5" t="n"/>
-      <c r="C144" s="2" t="n"/>
-      <c r="D144" s="2" t="n"/>
-      <c r="E144" s="6" t="n"/>
-      <c r="F144" s="7" t="n"/>
-    </row>
-    <row r="145" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A145" s="2" t="n"/>
-      <c r="B145" s="5" t="n"/>
-      <c r="C145" s="2" t="n"/>
-      <c r="D145" s="2" t="n"/>
-      <c r="E145" s="6" t="n"/>
-      <c r="F145" s="7" t="n"/>
-    </row>
-    <row r="146" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A146" s="2" t="n"/>
-      <c r="B146" s="5" t="n"/>
-      <c r="C146" s="2" t="n"/>
-      <c r="D146" s="2" t="n"/>
-      <c r="E146" s="6" t="n"/>
-      <c r="F146" s="7" t="n"/>
-    </row>
-    <row r="147" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A147" s="2" t="n"/>
-      <c r="B147" s="5" t="n"/>
-      <c r="C147" s="2" t="n"/>
-      <c r="D147" s="2" t="n"/>
-      <c r="E147" s="6" t="n"/>
-      <c r="F147" s="7" t="n"/>
-    </row>
-    <row r="148" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A148" s="2" t="n"/>
-      <c r="B148" s="5" t="n"/>
-      <c r="C148" s="2" t="n"/>
-      <c r="D148" s="2" t="n"/>
-      <c r="E148" s="6" t="n"/>
-      <c r="F148" s="7" t="n"/>
-    </row>
-    <row r="149" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A149" s="2" t="n"/>
-      <c r="B149" s="5" t="n"/>
-      <c r="C149" s="2" t="n"/>
-      <c r="D149" s="2" t="n"/>
-      <c r="E149" s="6" t="n"/>
-      <c r="F149" s="7" t="n"/>
-    </row>
-    <row r="150" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A150" s="2" t="n"/>
-      <c r="B150" s="5" t="n"/>
-      <c r="C150" s="2" t="n"/>
-      <c r="D150" s="2" t="n"/>
-      <c r="E150" s="6" t="n"/>
-      <c r="F150" s="7" t="n"/>
-    </row>
-    <row r="151" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A151" s="2" t="n"/>
-      <c r="B151" s="5" t="n"/>
-      <c r="C151" s="2" t="n"/>
-      <c r="D151" s="2" t="n"/>
-      <c r="E151" s="6" t="n"/>
-      <c r="F151" s="7" t="n"/>
-    </row>
-    <row r="152" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A152" s="2" t="n"/>
-      <c r="B152" s="5" t="n"/>
-      <c r="C152" s="2" t="n"/>
-      <c r="D152" s="2" t="n"/>
-      <c r="E152" s="6" t="n"/>
-      <c r="F152" s="7" t="n"/>
-    </row>
-    <row r="153" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A153" s="2" t="n"/>
-      <c r="B153" s="5" t="n"/>
-      <c r="C153" s="2" t="n"/>
-      <c r="D153" s="2" t="n"/>
-      <c r="E153" s="6" t="n"/>
-      <c r="F153" s="7" t="n"/>
-    </row>
-    <row r="154" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A154" s="2" t="n"/>
-      <c r="B154" s="5" t="n"/>
-      <c r="C154" s="2" t="n"/>
-      <c r="D154" s="2" t="n"/>
-      <c r="E154" s="6" t="n"/>
-      <c r="F154" s="7" t="n"/>
-    </row>
-    <row r="155" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A155" s="2" t="n"/>
-      <c r="B155" s="5" t="n"/>
-      <c r="C155" s="2" t="n"/>
-      <c r="D155" s="2" t="n"/>
-      <c r="E155" s="6" t="n"/>
-      <c r="F155" s="7" t="n"/>
-    </row>
-    <row r="156" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A156" s="2" t="n"/>
-      <c r="B156" s="5" t="n"/>
-      <c r="C156" s="2" t="n"/>
-      <c r="D156" s="2" t="n"/>
-      <c r="E156" s="6" t="n"/>
-      <c r="F156" s="7" t="n"/>
-    </row>
-    <row r="157" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A157" s="2" t="n"/>
-      <c r="B157" s="5" t="n"/>
-      <c r="C157" s="2" t="n"/>
-      <c r="D157" s="2" t="n"/>
-      <c r="E157" s="6" t="n"/>
-      <c r="F157" s="7" t="n"/>
-    </row>
-    <row r="158" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A158" s="2" t="n"/>
-      <c r="B158" s="5" t="n"/>
-      <c r="C158" s="2" t="n"/>
-      <c r="D158" s="2" t="n"/>
-      <c r="E158" s="6" t="n"/>
-      <c r="F158" s="7" t="n"/>
-    </row>
-    <row r="159" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A159" s="2" t="n"/>
-      <c r="B159" s="5" t="n"/>
-      <c r="C159" s="2" t="n"/>
-      <c r="D159" s="2" t="n"/>
-      <c r="E159" s="6" t="n"/>
-      <c r="F159" s="7" t="n"/>
-    </row>
-    <row r="160" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A160" s="2" t="n"/>
-      <c r="B160" s="5" t="n"/>
-      <c r="C160" s="2" t="n"/>
-      <c r="D160" s="2" t="n"/>
-      <c r="E160" s="6" t="n"/>
-      <c r="F160" s="7" t="n"/>
-    </row>
-    <row r="161" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A161" s="2" t="n"/>
-      <c r="B161" s="5" t="n"/>
-      <c r="C161" s="2" t="n"/>
-      <c r="D161" s="2" t="n"/>
-      <c r="E161" s="6" t="n"/>
-      <c r="F161" s="7" t="n"/>
-    </row>
-    <row r="162" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A162" s="2" t="n"/>
-      <c r="B162" s="5" t="n"/>
-      <c r="C162" s="2" t="n"/>
-      <c r="D162" s="2" t="n"/>
-      <c r="E162" s="6" t="n"/>
-      <c r="F162" s="7" t="n"/>
-    </row>
-    <row r="163" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A163" s="2" t="n"/>
-      <c r="B163" s="5" t="n"/>
-      <c r="C163" s="2" t="n"/>
-      <c r="D163" s="2" t="n"/>
-      <c r="E163" s="6" t="n"/>
-      <c r="F163" s="7" t="n"/>
-    </row>
-    <row r="164" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A164" s="2" t="n"/>
-      <c r="B164" s="5" t="n"/>
-      <c r="C164" s="2" t="n"/>
-      <c r="D164" s="2" t="n"/>
-      <c r="E164" s="6" t="n"/>
-      <c r="F164" s="7" t="n"/>
-    </row>
-    <row r="165" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A165" s="2" t="n"/>
-      <c r="B165" s="5" t="n"/>
-      <c r="C165" s="2" t="n"/>
-      <c r="D165" s="2" t="n"/>
-      <c r="E165" s="6" t="n"/>
-      <c r="F165" s="7" t="n"/>
-    </row>
-    <row r="166" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A166" s="2" t="n"/>
-      <c r="B166" s="5" t="n"/>
-      <c r="C166" s="2" t="n"/>
-      <c r="D166" s="2" t="n"/>
-      <c r="E166" s="6" t="n"/>
-      <c r="F166" s="7" t="n"/>
-    </row>
-    <row r="167" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A167" s="2" t="n"/>
-      <c r="B167" s="5" t="n"/>
-      <c r="C167" s="2" t="n"/>
-      <c r="D167" s="2" t="n"/>
-      <c r="E167" s="6" t="n"/>
-      <c r="F167" s="7" t="n"/>
-    </row>
-    <row r="168" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A168" s="2" t="n"/>
-      <c r="B168" s="5" t="n"/>
-      <c r="C168" s="2" t="n"/>
-      <c r="D168" s="2" t="n"/>
-      <c r="E168" s="6" t="n"/>
-      <c r="F168" s="7" t="n"/>
-    </row>
-    <row r="169" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A169" s="2" t="n"/>
-      <c r="B169" s="5" t="n"/>
-      <c r="C169" s="2" t="n"/>
-      <c r="D169" s="2" t="n"/>
-      <c r="E169" s="6" t="n"/>
-      <c r="F169" s="7" t="n"/>
-    </row>
-    <row r="170" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A170" s="2" t="n"/>
-      <c r="B170" s="5" t="n"/>
-      <c r="C170" s="2" t="n"/>
-      <c r="D170" s="2" t="n"/>
-      <c r="E170" s="6" t="n"/>
-      <c r="F170" s="7" t="n"/>
-    </row>
-    <row r="171" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A171" s="2" t="n"/>
-      <c r="B171" s="5" t="n"/>
-      <c r="C171" s="2" t="n"/>
-      <c r="D171" s="2" t="n"/>
-      <c r="E171" s="6" t="n"/>
-      <c r="F171" s="7" t="n"/>
-    </row>
-    <row r="172" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A172" s="2" t="n"/>
-      <c r="B172" s="5" t="n"/>
-      <c r="C172" s="2" t="n"/>
-      <c r="D172" s="2" t="n"/>
-      <c r="E172" s="6" t="n"/>
-      <c r="F172" s="7" t="n"/>
-    </row>
-    <row r="173" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A173" s="2" t="n"/>
-      <c r="B173" s="5" t="n"/>
-      <c r="C173" s="2" t="n"/>
-      <c r="D173" s="2" t="n"/>
-      <c r="E173" s="6" t="n"/>
-      <c r="F173" s="7" t="n"/>
-    </row>
-    <row r="174" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A174" s="2" t="n"/>
-      <c r="B174" s="5" t="n"/>
-      <c r="C174" s="2" t="n"/>
-      <c r="D174" s="2" t="n"/>
-      <c r="E174" s="6" t="n"/>
-      <c r="F174" s="7" t="n"/>
-    </row>
-    <row r="175" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A175" s="2" t="n"/>
-      <c r="B175" s="5" t="n"/>
-      <c r="C175" s="2" t="n"/>
-      <c r="D175" s="2" t="n"/>
-      <c r="E175" s="6" t="n"/>
-      <c r="F175" s="7" t="n"/>
-    </row>
-    <row r="176" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A176" s="2" t="n"/>
-      <c r="B176" s="5" t="n"/>
-      <c r="C176" s="2" t="n"/>
-      <c r="D176" s="2" t="n"/>
-      <c r="E176" s="6" t="n"/>
-      <c r="F176" s="7" t="n"/>
-    </row>
-    <row r="177" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A177" s="2" t="n"/>
-      <c r="B177" s="5" t="n"/>
-      <c r="C177" s="2" t="n"/>
-      <c r="D177" s="2" t="n"/>
-      <c r="E177" s="6" t="n"/>
-      <c r="F177" s="7" t="n"/>
-    </row>
-    <row r="178" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A178" s="2" t="n"/>
-      <c r="B178" s="5" t="n"/>
-      <c r="C178" s="2" t="n"/>
-      <c r="D178" s="2" t="n"/>
-      <c r="E178" s="6" t="n"/>
-      <c r="F178" s="7" t="n"/>
-    </row>
-    <row r="179" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A179" s="2" t="n"/>
-      <c r="B179" s="5" t="n"/>
-      <c r="C179" s="2" t="n"/>
-      <c r="D179" s="2" t="n"/>
-      <c r="E179" s="6" t="n"/>
-      <c r="F179" s="7" t="n"/>
-    </row>
-    <row r="180" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A180" s="2" t="n"/>
-      <c r="B180" s="5" t="n"/>
-      <c r="C180" s="2" t="n"/>
-      <c r="D180" s="2" t="n"/>
-      <c r="E180" s="6" t="n"/>
-      <c r="F180" s="7" t="n"/>
-    </row>
-    <row r="181" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A181" s="2" t="n"/>
-      <c r="B181" s="5" t="n"/>
-      <c r="C181" s="2" t="n"/>
-      <c r="D181" s="2" t="n"/>
-      <c r="E181" s="6" t="n"/>
-      <c r="F181" s="7" t="n"/>
-    </row>
-    <row r="182" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A182" s="2" t="n"/>
-      <c r="B182" s="5" t="n"/>
-      <c r="C182" s="2" t="n"/>
-      <c r="D182" s="2" t="n"/>
-      <c r="E182" s="6" t="n"/>
-      <c r="F182" s="7" t="n"/>
-    </row>
-    <row r="183" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A183" s="2" t="n"/>
-      <c r="B183" s="5" t="n"/>
-      <c r="C183" s="2" t="n"/>
-      <c r="D183" s="2" t="n"/>
-      <c r="E183" s="6" t="n"/>
-      <c r="F183" s="7" t="n"/>
-    </row>
-    <row r="184" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A184" s="2" t="n"/>
-      <c r="B184" s="5" t="n"/>
-      <c r="C184" s="2" t="n"/>
-      <c r="D184" s="2" t="n"/>
-      <c r="E184" s="6" t="n"/>
-      <c r="F184" s="7" t="n"/>
-    </row>
-    <row r="185" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A185" s="2" t="n"/>
-      <c r="B185" s="5" t="n"/>
-      <c r="C185" s="2" t="n"/>
-      <c r="D185" s="2" t="n"/>
-      <c r="E185" s="6" t="n"/>
-      <c r="F185" s="7" t="n"/>
-    </row>
-    <row r="186" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A186" s="2" t="n"/>
-      <c r="B186" s="5" t="n"/>
-      <c r="C186" s="2" t="n"/>
-      <c r="D186" s="2" t="n"/>
-      <c r="E186" s="6" t="n"/>
-      <c r="F186" s="7" t="n"/>
-    </row>
-    <row r="187" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A187" s="2" t="n"/>
-      <c r="B187" s="5" t="n"/>
-      <c r="C187" s="2" t="n"/>
-      <c r="D187" s="2" t="n"/>
-      <c r="E187" s="6" t="n"/>
-      <c r="F187" s="7" t="n"/>
-    </row>
-    <row r="188" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A188" s="2" t="n"/>
-      <c r="B188" s="5" t="n"/>
-      <c r="C188" s="2" t="n"/>
-      <c r="D188" s="2" t="n"/>
-      <c r="E188" s="6" t="n"/>
-      <c r="F188" s="7" t="n"/>
-    </row>
-    <row r="189" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A189" s="2" t="n"/>
-      <c r="B189" s="5" t="n"/>
-      <c r="C189" s="2" t="n"/>
-      <c r="D189" s="2" t="n"/>
-      <c r="E189" s="6" t="n"/>
-      <c r="F189" s="7" t="n"/>
-    </row>
-    <row r="190" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A190" s="2" t="n"/>
-      <c r="B190" s="5" t="n"/>
-      <c r="C190" s="2" t="n"/>
-      <c r="D190" s="2" t="n"/>
-      <c r="E190" s="6" t="n"/>
-      <c r="F190" s="7" t="n"/>
-    </row>
-    <row r="191" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A191" s="2" t="n"/>
-      <c r="B191" s="5" t="n"/>
-      <c r="C191" s="2" t="n"/>
-      <c r="D191" s="2" t="n"/>
-      <c r="E191" s="6" t="n"/>
-      <c r="F191" s="7" t="n"/>
-    </row>
-    <row r="192" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A192" s="2" t="n"/>
-      <c r="B192" s="5" t="n"/>
-      <c r="C192" s="2" t="n"/>
-      <c r="D192" s="2" t="n"/>
-      <c r="E192" s="6" t="n"/>
-      <c r="F192" s="7" t="n"/>
-    </row>
-    <row r="193" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A193" s="2" t="n"/>
-      <c r="B193" s="5" t="n"/>
-      <c r="C193" s="2" t="n"/>
-      <c r="D193" s="2" t="n"/>
-      <c r="E193" s="6" t="n"/>
-      <c r="F193" s="7" t="n"/>
-    </row>
-    <row r="194" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A194" s="2" t="n"/>
-      <c r="B194" s="5" t="n"/>
-      <c r="C194" s="2" t="n"/>
-      <c r="D194" s="2" t="n"/>
-      <c r="E194" s="6" t="n"/>
-      <c r="F194" s="7" t="n"/>
-    </row>
-    <row r="195" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A195" s="2" t="n"/>
-      <c r="B195" s="5" t="n"/>
-      <c r="C195" s="2" t="n"/>
-      <c r="D195" s="2" t="n"/>
-      <c r="E195" s="6" t="n"/>
-      <c r="F195" s="7" t="n"/>
-    </row>
-    <row r="196" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A196" s="2" t="n"/>
-      <c r="B196" s="5" t="n"/>
-      <c r="C196" s="2" t="n"/>
-      <c r="D196" s="2" t="n"/>
-      <c r="E196" s="6" t="n"/>
-      <c r="F196" s="7" t="n"/>
-    </row>
-    <row r="197" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A197" s="2" t="n"/>
-      <c r="B197" s="5" t="n"/>
-      <c r="C197" s="2" t="n"/>
-      <c r="D197" s="2" t="n"/>
-      <c r="E197" s="6" t="n"/>
-      <c r="F197" s="7" t="n"/>
-    </row>
-    <row r="198" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A198" s="2" t="n"/>
-      <c r="B198" s="5" t="n"/>
-      <c r="C198" s="2" t="n"/>
-      <c r="D198" s="2" t="n"/>
-      <c r="E198" s="6" t="n"/>
-      <c r="F198" s="7" t="n"/>
-    </row>
-    <row r="199" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A199" s="2" t="n"/>
-      <c r="B199" s="5" t="n"/>
-      <c r="C199" s="2" t="n"/>
-      <c r="D199" s="2" t="n"/>
-      <c r="E199" s="6" t="n"/>
-      <c r="F199" s="7" t="n"/>
-    </row>
-    <row r="200" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A200" s="2" t="n"/>
-      <c r="B200" s="5" t="n"/>
-      <c r="C200" s="2" t="n"/>
-      <c r="D200" s="2" t="n"/>
-      <c r="E200" s="6" t="n"/>
-      <c r="F200" s="7" t="n"/>
-    </row>
-    <row r="201" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A201" s="2" t="n"/>
-      <c r="B201" s="5" t="n"/>
-      <c r="C201" s="2" t="n"/>
-      <c r="D201" s="2" t="n"/>
-      <c r="E201" s="6" t="n"/>
-      <c r="F201" s="7" t="n"/>
-    </row>
-    <row r="202" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A202" s="2" t="n"/>
-      <c r="B202" s="5" t="n"/>
-      <c r="C202" s="2" t="n"/>
-      <c r="D202" s="2" t="n"/>
-      <c r="E202" s="6" t="n"/>
-      <c r="F202" s="7" t="n"/>
-    </row>
-    <row r="203" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A203" s="2" t="n"/>
-      <c r="B203" s="5" t="n"/>
-      <c r="C203" s="2" t="n"/>
-      <c r="D203" s="2" t="n"/>
-      <c r="E203" s="6" t="n"/>
-      <c r="F203" s="7" t="n"/>
-    </row>
-    <row r="204" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A204" s="2" t="n"/>
-      <c r="B204" s="5" t="n"/>
-      <c r="C204" s="2" t="n"/>
-      <c r="D204" s="2" t="n"/>
-      <c r="E204" s="6" t="n"/>
-      <c r="F204" s="7" t="n"/>
-    </row>
-    <row r="205" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A205" s="2" t="n"/>
-      <c r="B205" s="5" t="n"/>
-      <c r="C205" s="2" t="n"/>
-      <c r="D205" s="2" t="n"/>
-      <c r="E205" s="6" t="n"/>
-      <c r="F205" s="7" t="n"/>
-    </row>
-    <row r="206" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A206" s="2" t="n"/>
-      <c r="B206" s="5" t="n"/>
-      <c r="C206" s="2" t="n"/>
-      <c r="D206" s="2" t="n"/>
-      <c r="E206" s="6" t="n"/>
-      <c r="F206" s="7" t="n"/>
-    </row>
-    <row r="207" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A207" s="2" t="n"/>
-      <c r="B207" s="5" t="n"/>
-      <c r="C207" s="2" t="n"/>
-      <c r="D207" s="2" t="n"/>
-      <c r="E207" s="6" t="n"/>
-      <c r="F207" s="7" t="n"/>
-    </row>
-    <row r="208" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A208" s="2" t="n"/>
-      <c r="B208" s="5" t="n"/>
-      <c r="C208" s="2" t="n"/>
-      <c r="D208" s="2" t="n"/>
-      <c r="E208" s="6" t="n"/>
-      <c r="F208" s="7" t="n"/>
-    </row>
-    <row r="209" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A209" s="2" t="n"/>
-      <c r="B209" s="5" t="n"/>
-      <c r="C209" s="2" t="n"/>
-      <c r="D209" s="2" t="n"/>
-      <c r="E209" s="6" t="n"/>
-      <c r="F209" s="7" t="n"/>
-    </row>
-    <row r="210" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A210" s="2" t="n"/>
-      <c r="B210" s="5" t="n"/>
-      <c r="C210" s="2" t="n"/>
-      <c r="D210" s="2" t="n"/>
-      <c r="E210" s="6" t="n"/>
-      <c r="F210" s="7" t="n"/>
-    </row>
-    <row r="211" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A211" s="2" t="n"/>
-      <c r="B211" s="5" t="n"/>
-      <c r="C211" s="2" t="n"/>
-      <c r="D211" s="2" t="n"/>
-      <c r="E211" s="6" t="n"/>
-      <c r="F211" s="7" t="n"/>
-    </row>
-    <row r="212" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A212" s="2" t="n"/>
-      <c r="B212" s="5" t="n"/>
-      <c r="C212" s="2" t="n"/>
-      <c r="D212" s="2" t="n"/>
-      <c r="E212" s="6" t="n"/>
-      <c r="F212" s="7" t="n"/>
-    </row>
-    <row r="213" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A213" s="2" t="n"/>
-      <c r="B213" s="5" t="n"/>
-      <c r="C213" s="2" t="n"/>
-      <c r="D213" s="2" t="n"/>
-      <c r="E213" s="6" t="n"/>
-      <c r="F213" s="7" t="n"/>
-    </row>
-    <row r="214" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A214" s="2" t="n"/>
-      <c r="B214" s="5" t="n"/>
-      <c r="C214" s="2" t="n"/>
-      <c r="D214" s="2" t="n"/>
-      <c r="E214" s="6" t="n"/>
-      <c r="F214" s="7" t="n"/>
-    </row>
-    <row r="215" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A215" s="2" t="n"/>
-      <c r="B215" s="5" t="n"/>
-      <c r="C215" s="2" t="n"/>
-      <c r="D215" s="2" t="n"/>
-      <c r="E215" s="6" t="n"/>
-      <c r="F215" s="7" t="n"/>
-    </row>
-    <row r="216" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A216" s="2" t="n"/>
-      <c r="B216" s="5" t="n"/>
-      <c r="C216" s="2" t="n"/>
-      <c r="D216" s="2" t="n"/>
-      <c r="E216" s="6" t="n"/>
-      <c r="F216" s="7" t="n"/>
-    </row>
-    <row r="217" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A217" s="2" t="n"/>
-      <c r="B217" s="5" t="n"/>
-      <c r="C217" s="2" t="n"/>
-      <c r="D217" s="2" t="n"/>
-      <c r="E217" s="6" t="n"/>
-      <c r="F217" s="7" t="n"/>
-    </row>
-    <row r="218" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A218" s="2" t="n"/>
-      <c r="B218" s="5" t="n"/>
-      <c r="C218" s="2" t="n"/>
-      <c r="D218" s="2" t="n"/>
-      <c r="E218" s="6" t="n"/>
-      <c r="F218" s="7" t="n"/>
-    </row>
-    <row r="219" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A219" s="2" t="n"/>
-      <c r="B219" s="5" t="n"/>
-      <c r="C219" s="2" t="n"/>
-      <c r="D219" s="2" t="n"/>
-      <c r="E219" s="6" t="n"/>
-      <c r="F219" s="7" t="n"/>
-    </row>
-    <row r="220" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A220" s="2" t="n"/>
-      <c r="B220" s="5" t="n"/>
-      <c r="C220" s="2" t="n"/>
-      <c r="D220" s="2" t="n"/>
-      <c r="E220" s="6" t="n"/>
-      <c r="F220" s="7" t="n"/>
-    </row>
-    <row r="221" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A221" s="2" t="n"/>
-      <c r="B221" s="5" t="n"/>
-      <c r="C221" s="2" t="n"/>
-      <c r="D221" s="2" t="n"/>
-      <c r="E221" s="6" t="n"/>
-      <c r="F221" s="7" t="n"/>
-    </row>
-    <row r="222" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A222" s="2" t="n"/>
-      <c r="B222" s="5" t="n"/>
-      <c r="C222" s="2" t="n"/>
-      <c r="D222" s="2" t="n"/>
-      <c r="E222" s="6" t="n"/>
-      <c r="F222" s="7" t="n"/>
-    </row>
-    <row r="223" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A223" s="2" t="n"/>
-      <c r="B223" s="5" t="n"/>
-      <c r="C223" s="2" t="n"/>
-      <c r="D223" s="2" t="n"/>
-      <c r="E223" s="6" t="n"/>
-      <c r="F223" s="7" t="n"/>
-    </row>
-    <row r="224" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A224" s="2" t="n"/>
-      <c r="B224" s="5" t="n"/>
-      <c r="C224" s="2" t="n"/>
-      <c r="D224" s="2" t="n"/>
-      <c r="E224" s="6" t="n"/>
-      <c r="F224" s="7" t="n"/>
-    </row>
-    <row r="225" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A225" s="2" t="n"/>
-      <c r="B225" s="5" t="n"/>
-      <c r="C225" s="2" t="n"/>
-      <c r="D225" s="2" t="n"/>
-      <c r="E225" s="6" t="n"/>
-      <c r="F225" s="7" t="n"/>
-    </row>
-    <row r="226" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A226" s="2" t="n"/>
-      <c r="B226" s="5" t="n"/>
-      <c r="C226" s="2" t="n"/>
-      <c r="D226" s="2" t="n"/>
-      <c r="E226" s="6" t="n"/>
-      <c r="F226" s="7" t="n"/>
-    </row>
-    <row r="227" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A227" s="2" t="n"/>
-      <c r="B227" s="5" t="n"/>
-      <c r="C227" s="2" t="n"/>
-      <c r="D227" s="2" t="n"/>
-      <c r="E227" s="6" t="n"/>
-      <c r="F227" s="7" t="n"/>
-    </row>
-    <row r="228" hidden="1" ht="60" customHeight="1" thickBot="1">
-      <c r="A228" s="2" t="n"/>
-      <c r="B228" s="5" t="n"/>
-      <c r="C228" s="2" t="n"/>
-      <c r="D228" s="2" t="n"/>
-      <c r="E228" s="6" t="n"/>
-      <c r="F228" s="7" t="n"/>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>36-37367</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="60" customHeight="1" thickBot="1">
+      <c r="A71" s="2" t="n">
+        <v>4387</v>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>46041</v>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>حمزة القبلاني</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>46-11634</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="60" customHeight="1" thickBot="1">
+      <c r="A72" s="2" t="n">
+        <v>4389</v>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>46041</v>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>محمود الخضر</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>11-355</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="60" customHeight="1" thickBot="1">
+      <c r="A73" s="2" t="n">
+        <v>4398</v>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>46042</v>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>انس ابو عودة</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>11-685</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="60" customHeight="1" thickBot="1">
+      <c r="A74" s="2" t="n">
+        <v>4407</v>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>46043</v>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>غسان الوحوش</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>46-12472</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="60" customHeight="1" thickBot="1">
+      <c r="A75" s="2" t="n">
+        <v>4411</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>46043</v>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>غسان خوري</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>46-15033</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="60" customHeight="1" thickBot="1">
+      <c r="A76" s="2" t="n">
+        <v>4420</v>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>46044</v>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>نادي الرياضات الجوي الملكي الاردني</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="60" customHeight="1" thickBot="1">
+      <c r="A77" s="2" t="n">
+        <v>4444</v>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>46047</v>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>حسن وهداني</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>48-85568</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="60" customHeight="1" thickBot="1">
+      <c r="A78" s="2" t="n">
+        <v>4460</v>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>46049</v>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Gulf agency company</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>qae 1200</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="60" customHeight="1" thickBot="1">
+      <c r="A79" s="2" t="n">
+        <v>4469</v>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>46050</v>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>كنج شكري</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>42-84886</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="60" customHeight="1" thickBot="1">
+      <c r="A80" s="2" t="n">
+        <v>4470</v>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>46050</v>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>عاصم</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>48-54476</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="60" customHeight="1" thickBot="1">
+      <c r="A81" s="2" t="n">
+        <v>4493</v>
+      </c>
+      <c r="B81" s="5" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>شفيق حايك</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>44-23977</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="60" customHeight="1" thickBot="1">
+      <c r="A82" s="2" t="n">
+        <v>4494</v>
+      </c>
+      <c r="B82" s="5" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>وسام العبادي</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>45-90187</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="60" customHeight="1" thickBot="1">
+      <c r="A83" s="2" t="n">
+        <v>4495</v>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>رمزي شكري</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>80-7809</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="60" customHeight="1" thickBot="1">
+      <c r="A84" s="2" t="n">
+        <v>4496</v>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>نيكولا عدس</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="n">
+        <v>125</v>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t>46-13463 , 46-10313</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="60" customHeight="1" thickBot="1">
+      <c r="A85" s="2" t="n">
+        <v>4506</v>
+      </c>
+      <c r="B85" s="5" t="n">
+        <v>46055</v>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>منير صوبر</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>JJBVWAW2XJK000099</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="60" customHeight="1" thickBot="1">
+      <c r="A86" s="2" t="n">
+        <v>4507</v>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>46055</v>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>سمير السامرائي</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>45-39121</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="60" customHeight="1" thickBot="1">
+      <c r="A87" s="2" t="n">
+        <v>4508</v>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>46055</v>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>حازم خرفان</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>47-78388</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="60" customHeight="1" thickBot="1">
+      <c r="A88" s="2" t="n">
+        <v>4511</v>
+      </c>
+      <c r="B88" s="5" t="n">
+        <v>46055</v>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>رمزي خربط</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>46-88679</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="60" customHeight="1" thickBot="1">
+      <c r="A89" s="2" t="n">
+        <v>4515</v>
+      </c>
+      <c r="B89" s="5" t="n">
+        <v>46056</v>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>مهاب بسطامي</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>41-1440</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="60" customHeight="1" thickBot="1">
+      <c r="A90" s="2" t="n">
+        <v>4517</v>
+      </c>
+      <c r="B90" s="5" t="n">
+        <v>46056</v>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>معرض القلم</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>ازرق</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="60" customHeight="1" thickBot="1">
+      <c r="A91" s="2" t="n">
+        <v>4525</v>
+      </c>
+      <c r="B91" s="5" t="n">
+        <v>46056</v>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>ايمن سلطان</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>46-13735</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="60" customHeight="1" thickBot="1">
+      <c r="A92" s="2" t="n">
+        <v>4551</v>
+      </c>
+      <c r="B92" s="5" t="n">
+        <v>46058</v>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>ابراهيم العمري</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>46-10962</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="60" customHeight="1" thickBot="1">
+      <c r="A93" s="2" t="n">
+        <v>4553</v>
+      </c>
+      <c r="B93" s="5" t="n">
+        <v>46060</v>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>خالد كمال</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>46-15749</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="60" customHeight="1" thickBot="1">
+      <c r="A94" s="2" t="n">
+        <v>4562</v>
+      </c>
+      <c r="B94" s="5" t="n">
+        <v>46060</v>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>محمود كنعان</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F94" s="7" t="inlineStr">
+        <is>
+          <t>46-16409</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="60" customHeight="1" thickBot="1">
+      <c r="A95" s="2" t="n">
+        <v>4583</v>
+      </c>
+      <c r="B95" s="5" t="n">
+        <v>46061</v>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>حكمت قطامين</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="n">
+        <v>115</v>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>46-10962</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="60" customHeight="1" thickBot="1">
+      <c r="A96" s="2" t="n">
+        <v>4585</v>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>46062</v>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>ليما الشنقيطي</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F96" s="7" t="inlineStr">
+        <is>
+          <t>36-70267</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="60" customHeight="1" thickBot="1">
+      <c r="A97" s="2" t="n">
+        <v>4593</v>
+      </c>
+      <c r="B97" s="5" t="n">
+        <v>46062</v>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>فريز النابلسي</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>46-12462</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="60" customHeight="1" thickBot="1">
+      <c r="A98" s="2" t="n">
+        <v>4609</v>
+      </c>
+      <c r="B98" s="5" t="n">
+        <v>46063</v>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>ابو علاء</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="F98" s="7" t="inlineStr">
+        <is>
+          <t>18-1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="60" customHeight="1" thickBot="1">
+      <c r="A99" s="2" t="n">
+        <v>4667</v>
+      </c>
+      <c r="B99" s="5" t="n">
+        <v>46069</v>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>ينال ابو الرب</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>49-61752</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="60" customHeight="1" thickBot="1">
+      <c r="A100" s="2" t="n">
+        <v>4674</v>
+      </c>
+      <c r="B100" s="5" t="n">
+        <v>46069</v>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>محمود كنعان</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F100" s="7" t="inlineStr">
+        <is>
+          <t>46-16409</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="60" customHeight="1" thickBot="1">
+      <c r="A101" s="2" t="n">
+        <v>4686</v>
+      </c>
+      <c r="B101" s="5" t="n">
+        <v>46070</v>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>نادي السيارات الملكي</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F101" s="7" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="60" customHeight="1" thickBot="1">
+      <c r="A102" s="2" t="n">
+        <v>4687</v>
+      </c>
+      <c r="B102" s="5" t="n">
+        <v>46070</v>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>نادي السيارات الملكي</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F102" s="7" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="60" customHeight="1" thickBot="1">
+      <c r="A103" s="2" t="n">
+        <v>4689</v>
+      </c>
+      <c r="B103" s="5" t="n">
+        <v>46070</v>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>نادي السيارات الملكي</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="60" customHeight="1" thickBot="1">
+      <c r="A104" s="2" t="n">
+        <v>4690</v>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>46070</v>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>نادي السيارات الملكي</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F104" s="7" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="60" customHeight="1" thickBot="1">
+      <c r="A105" s="2" t="n">
+        <v>4691</v>
+      </c>
+      <c r="B105" s="5" t="n">
+        <v>46070</v>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>نادي السيارات الملكي</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="60" customHeight="1" thickBot="1">
+      <c r="A106" s="2" t="n">
+        <v>4713</v>
+      </c>
+      <c r="B106" s="5" t="n">
+        <v>46071</v>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>مهاب بسطامي</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
+          <t>41-1440</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="60" customHeight="1" thickBot="1">
+      <c r="A107" s="2" t="n">
+        <v>4718</v>
+      </c>
+      <c r="B107" s="5" t="n">
+        <v>46071</v>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>اسامة كاجو</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>46-13118</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="60" customHeight="1" thickBot="1">
+      <c r="A108" s="2" t="n">
+        <v>4725</v>
+      </c>
+      <c r="B108" s="5" t="n">
+        <v>46072</v>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>جهاد</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>40-91886</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="60" customHeight="1" thickBot="1">
+      <c r="A109" s="2" t="n">
+        <v>4739</v>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>46074</v>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>عمر خيامي</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
+          <t>46-11946</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="60" customHeight="1" thickBot="1">
+      <c r="A110" s="2" t="n">
+        <v>4763</v>
+      </c>
+      <c r="B110" s="5" t="n">
+        <v>46076</v>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>نادي السيارات الملكي</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F110" s="7" t="inlineStr">
+        <is>
+          <t>4556</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="60" customHeight="1" thickBot="1">
+      <c r="A111" s="2" t="n">
+        <v>4768</v>
+      </c>
+      <c r="B111" s="5" t="n">
+        <v>46076</v>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>غسان حلاوة</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F111" s="7" t="inlineStr">
+        <is>
+          <t>46-4647</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="60" customHeight="1" thickBot="1">
+      <c r="A112" s="2" t="n">
+        <v>4778</v>
+      </c>
+      <c r="B112" s="5" t="n">
+        <v>46077</v>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>غسان حلاوة</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F112" s="7" t="inlineStr">
+        <is>
+          <t>48-4647</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="60" customHeight="1" thickBot="1">
+      <c r="A113" s="2" t="n">
+        <v>4806</v>
+      </c>
+      <c r="B113" s="5" t="n">
+        <v>46079</v>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>تيمور الموج</t>
+        </is>
+      </c>
+      <c r="E113" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F113" s="7" t="inlineStr">
+        <is>
+          <t>46-11415</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="60" customHeight="1" thickBot="1">
+      <c r="A114" s="2" t="n">
+        <v>4815</v>
+      </c>
+      <c r="B114" s="5" t="n">
+        <v>46081</v>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>وائل صفوري</t>
+        </is>
+      </c>
+      <c r="E114" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F114" s="7" t="inlineStr">
+        <is>
+          <t>46-14165</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="60" customHeight="1" thickBot="1">
+      <c r="A115" s="2" t="n">
+        <v>4852</v>
+      </c>
+      <c r="B115" s="5" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>احمد خطاب</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F115" s="7" t="inlineStr">
+        <is>
+          <t>30-3141 , 46-14259</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="60" customHeight="1" thickBot="1">
+      <c r="A116" s="2" t="n">
+        <v>4855</v>
+      </c>
+      <c r="B116" s="5" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>قيس شعبان</t>
+        </is>
+      </c>
+      <c r="E116" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F116" s="7" t="inlineStr">
+        <is>
+          <t>36-62570</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="60" customHeight="1" thickBot="1">
+      <c r="A117" s="2" t="n">
+        <v>4873</v>
+      </c>
+      <c r="B117" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>نادي السيارات الملكي</t>
+        </is>
+      </c>
+      <c r="E117" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F117" s="7" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="60" customHeight="1" thickBot="1">
+      <c r="A118" s="2" t="n">
+        <v>4884</v>
+      </c>
+      <c r="B118" s="5" t="n">
+        <v>46084</v>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>عمرمعاذ</t>
+        </is>
+      </c>
+      <c r="E118" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F118" s="7" t="inlineStr">
+        <is>
+          <t>46-14867</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="60" customHeight="1" thickBot="1">
+      <c r="A119" s="2" t="n">
+        <v>4888</v>
+      </c>
+      <c r="B119" s="5" t="n">
+        <v>46084</v>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>وائل صفوري</t>
+        </is>
+      </c>
+      <c r="E119" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F119" s="7" t="inlineStr">
+        <is>
+          <t>46-14156</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="60" customHeight="1" thickBot="1">
+      <c r="A120" s="2" t="n">
+        <v>4914</v>
+      </c>
+      <c r="B120" s="5" t="n">
+        <v>46086</v>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>نيكولا عزوني</t>
+        </is>
+      </c>
+      <c r="E120" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F120" s="7" t="inlineStr">
+        <is>
+          <t>31512</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="60" customHeight="1" thickBot="1">
+      <c r="A121" s="2" t="n">
+        <v>4929</v>
+      </c>
+      <c r="B121" s="5" t="n">
+        <v>46088</v>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>جبريل ابراهيم</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F121" s="7" t="inlineStr">
+        <is>
+          <t>66-15199</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="60" customHeight="1" thickBot="1">
+      <c r="A122" s="2" t="n">
+        <v>4941</v>
+      </c>
+      <c r="B122" s="5" t="n">
+        <v>46090</v>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>محمد الكردي</t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F122" s="7" t="inlineStr">
+        <is>
+          <t>46-16037</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="60" customHeight="1" thickBot="1">
+      <c r="A123" s="2" t="n">
+        <v>4955</v>
+      </c>
+      <c r="B123" s="5" t="n">
+        <v>46091</v>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>طارق عواودة</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F123" s="7" t="inlineStr">
+        <is>
+          <t>46-95913</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="60" customHeight="1" thickBot="1">
+      <c r="A124" s="2" t="n">
+        <v>4969</v>
+      </c>
+      <c r="B124" s="5" t="n">
+        <v>46092</v>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>اسامة كاجو</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F124" s="7" t="inlineStr">
+        <is>
+          <t>46-13118</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="60" customHeight="1" thickBot="1">
+      <c r="A125" s="2" t="n">
+        <v>4972</v>
+      </c>
+      <c r="B125" s="5" t="n">
+        <v>46092</v>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>الشركة الاردنية العالمية للدراجات النارية</t>
+        </is>
+      </c>
+      <c r="E125" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F125" s="7" t="inlineStr">
+        <is>
+          <t>66-24959</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="60" customHeight="1" thickBot="1">
+      <c r="A126" s="2" t="n">
+        <v>5003</v>
+      </c>
+      <c r="B126" s="5" t="n">
+        <v>46096</v>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>فرانكو</t>
+        </is>
+      </c>
+      <c r="E126" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="F126" s="7" t="inlineStr">
+        <is>
+          <t>44-92455</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="60" customHeight="1" thickBot="1">
+      <c r="A127" s="2" t="n">
+        <v>5011</v>
+      </c>
+      <c r="B127" s="5" t="n">
+        <v>46096</v>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>امير ابو صيني</t>
+        </is>
+      </c>
+      <c r="E127" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F127" s="7" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="60" customHeight="1" thickBot="1">
+      <c r="A128" s="2" t="n">
+        <v>5022</v>
+      </c>
+      <c r="B128" s="5" t="n">
+        <v>46097</v>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>شركة الافضل</t>
+        </is>
+      </c>
+      <c r="E128" s="6" t="n">
+        <v>170</v>
+      </c>
+      <c r="F128" s="7" t="inlineStr">
+        <is>
+          <t>37-95802</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="60" customHeight="1" thickBot="1">
+      <c r="A129" s="2" t="n">
+        <v>5035</v>
+      </c>
+      <c r="B129" s="5" t="n">
+        <v>46098</v>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>فيكتور حنوش</t>
+        </is>
+      </c>
+      <c r="E129" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F129" s="7" t="inlineStr">
+        <is>
+          <t>46-12635</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="60" customHeight="1" thickBot="1">
+      <c r="A130" s="2" t="n">
+        <v>5042</v>
+      </c>
+      <c r="B130" s="5" t="n">
+        <v>46098</v>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>رمزي خربط</t>
+        </is>
+      </c>
+      <c r="E130" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F130" s="7" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="60" customHeight="1" thickBot="1">
+      <c r="A131" s="2" t="n">
+        <v>5052</v>
+      </c>
+      <c r="B131" s="5" t="n">
+        <v>46099</v>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>رمزي شكري</t>
+        </is>
+      </c>
+      <c r="E131" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F131" s="7" t="inlineStr">
+        <is>
+          <t>80-7809</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="60" customHeight="1" thickBot="1">
+      <c r="A132" s="2" t="n">
+        <v>5067</v>
+      </c>
+      <c r="B132" s="5" t="n">
+        <v>46100</v>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>حسام مطر</t>
+        </is>
+      </c>
+      <c r="E132" s="6" t="n">
+        <v>25.01</v>
+      </c>
+      <c r="F132" s="7" t="inlineStr">
+        <is>
+          <t>46-11932</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="60" customHeight="1" thickBot="1">
+      <c r="A133" s="2" t="n">
+        <v>5077</v>
+      </c>
+      <c r="B133" s="5" t="n">
+        <v>46104</v>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>رمزي خربط</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F133" s="7" t="inlineStr">
+        <is>
+          <t>46-88679</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="60" customHeight="1" thickBot="1">
+      <c r="A134" s="2" t="n">
+        <v>5086</v>
+      </c>
+      <c r="B134" s="5" t="n">
+        <v>46105</v>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>احمد ابو طويلة</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="n">
+        <v>170</v>
+      </c>
+      <c r="F134" s="7" t="inlineStr">
+        <is>
+          <t>46-12706</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="60" customHeight="1" thickBot="1">
+      <c r="A135" s="2" t="n">
+        <v>5096</v>
+      </c>
+      <c r="B135" s="5" t="n">
+        <v>46106</v>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>عمر حماد</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F135" s="7" t="inlineStr">
+        <is>
+          <t>66-97822</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="60" customHeight="1" thickBot="1">
+      <c r="A136" s="2" t="n">
+        <v>5097</v>
+      </c>
+      <c r="B136" s="5" t="n">
+        <v>46106</v>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>حسام مطر</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F136" s="7" t="inlineStr">
+        <is>
+          <t>66-97822</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="60" customHeight="1" thickBot="1">
+      <c r="A137" s="2" t="n">
+        <v>5112</v>
+      </c>
+      <c r="B137" s="5" t="n">
+        <v>46107</v>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>فهد المصري</t>
+        </is>
+      </c>
+      <c r="E137" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F137" s="7" t="inlineStr">
+        <is>
+          <t>46-10798</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="60" customHeight="1" thickBot="1">
+      <c r="A138" s="2" t="n">
+        <v>5135</v>
+      </c>
+      <c r="B138" s="5" t="n">
+        <v>46110</v>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>سليمان الجدي</t>
+        </is>
+      </c>
+      <c r="E138" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="F138" s="7" t="inlineStr">
+        <is>
+          <t>45-3721</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="60" customHeight="1" thickBot="1">
+      <c r="A139" s="2" t="n">
+        <v>5140</v>
+      </c>
+      <c r="B139" s="5" t="n">
+        <v>46110</v>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>مهاب بسطامي</t>
+        </is>
+      </c>
+      <c r="E139" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="F139" s="7" t="inlineStr">
+        <is>
+          <t>11-1328</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="60" customHeight="1" thickBot="1">
+      <c r="A140" s="2" t="n">
+        <v>5146</v>
+      </c>
+      <c r="B140" s="5" t="n">
+        <v>46111</v>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>الشريف جميل بن ناصر</t>
+        </is>
+      </c>
+      <c r="E140" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="F140" s="7" t="inlineStr">
+        <is>
+          <t>46-98974</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="60" customHeight="1" thickBot="1">
+      <c r="A141" s="2" t="n">
+        <v>5163</v>
+      </c>
+      <c r="B141" s="5" t="n">
+        <v>46112</v>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>خالد الهواري</t>
+        </is>
+      </c>
+      <c r="E141" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F141" s="7" t="inlineStr">
+        <is>
+          <t>47-83440</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="60" customHeight="1" thickBot="1">
+      <c r="A142" s="2" t="n">
+        <v>5185</v>
+      </c>
+      <c r="B142" s="5" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>محمد بدار</t>
+        </is>
+      </c>
+      <c r="E142" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F142" s="7" t="inlineStr">
+        <is>
+          <t>46-11833</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="60" customHeight="1" thickBot="1">
+      <c r="A143" s="2" t="n">
+        <v>5194</v>
+      </c>
+      <c r="B143" s="5" t="n">
+        <v>46116</v>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>وليد هزاع</t>
+        </is>
+      </c>
+      <c r="E143" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F143" s="7" t="inlineStr">
+        <is>
+          <t>37-52760</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="60" customHeight="1" thickBot="1">
+      <c r="A144" s="2" t="n">
+        <v>5199</v>
+      </c>
+      <c r="B144" s="5" t="n">
+        <v>46116</v>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>مؤيد مجلي</t>
+        </is>
+      </c>
+      <c r="E144" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F144" s="7" t="inlineStr">
+        <is>
+          <t>45-20332</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="60" customHeight="1" thickBot="1">
+      <c r="A145" s="2" t="n">
+        <v>5217</v>
+      </c>
+      <c r="B145" s="5" t="n">
+        <v>46117</v>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>انس ابو عودة</t>
+        </is>
+      </c>
+      <c r="E145" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F145" s="7" t="inlineStr">
+        <is>
+          <t>11-685</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="60" customHeight="1" thickBot="1">
+      <c r="A146" s="2" t="n">
+        <v>5222</v>
+      </c>
+      <c r="B146" s="5" t="n">
+        <v>46118</v>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>مؤيد مجلي</t>
+        </is>
+      </c>
+      <c r="E146" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F146" s="7" t="inlineStr">
+        <is>
+          <t>45_20332</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="60" customHeight="1" thickBot="1">
+      <c r="A147" s="2" t="n">
+        <v>5225</v>
+      </c>
+      <c r="B147" s="5" t="n">
+        <v>46118</v>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>رمزي خربط</t>
+        </is>
+      </c>
+      <c r="E147" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F147" s="7" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="60" customHeight="1" thickBot="1">
+      <c r="A148" s="2" t="n">
+        <v>5238</v>
+      </c>
+      <c r="B148" s="5" t="n">
+        <v>46119</v>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>ظافر المصري</t>
+        </is>
+      </c>
+      <c r="E148" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F148" s="7" t="inlineStr">
+        <is>
+          <t>36-43551</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="60" customHeight="1" thickBot="1">
+      <c r="A149" s="2" t="n">
+        <v>5271</v>
+      </c>
+      <c r="B149" s="5" t="n">
+        <v>46121</v>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>تامبي قناش</t>
+        </is>
+      </c>
+      <c r="E149" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F149" s="7" t="inlineStr">
+        <is>
+          <t>48_31873</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="60" customHeight="1" thickBot="1">
+      <c r="A150" s="2" t="n">
+        <v>5278</v>
+      </c>
+      <c r="B150" s="5" t="n">
+        <v>46121</v>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>أبو سلوم موتورز</t>
+        </is>
+      </c>
+      <c r="E150" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F150" s="7" t="inlineStr">
+        <is>
+          <t>SALKP9FU5SA279454 , JTJGD7CX3S4004511</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="60" customHeight="1" thickBot="1">
+      <c r="A151" s="2" t="n">
+        <v>5279</v>
+      </c>
+      <c r="B151" s="5" t="n">
+        <v>46123</v>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>طارق احمد</t>
+        </is>
+      </c>
+      <c r="E151" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F151" s="7" t="inlineStr">
+        <is>
+          <t>37-81875</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="60" customHeight="1" thickBot="1">
+      <c r="A152" s="2" t="n">
+        <v>5283</v>
+      </c>
+      <c r="B152" s="5" t="n">
+        <v>46123</v>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>عمران بدر</t>
+        </is>
+      </c>
+      <c r="E152" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F152" s="7" t="inlineStr">
+        <is>
+          <t>47-15448</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="60" customHeight="1" thickBot="1">
+      <c r="A153" s="2" t="n">
+        <v>5287</v>
+      </c>
+      <c r="B153" s="5" t="n">
+        <v>46124</v>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>مأمون زهران</t>
+        </is>
+      </c>
+      <c r="E153" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F153" s="7" t="inlineStr">
+        <is>
+          <t>46-11742</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="60" customHeight="1" thickBot="1">
+      <c r="A154" s="2" t="n">
+        <v>5288</v>
+      </c>
+      <c r="B154" s="5" t="n">
+        <v>46124</v>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>طارق مشربش</t>
+        </is>
+      </c>
+      <c r="E154" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F154" s="7" t="inlineStr">
+        <is>
+          <t>23-86633</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="60" customHeight="1" thickBot="1">
+      <c r="A155" s="2" t="n">
+        <v>5300</v>
+      </c>
+      <c r="B155" s="5" t="n">
+        <v>46126</v>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>زياد حنانيا</t>
+        </is>
+      </c>
+      <c r="E155" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F155" s="7" t="inlineStr">
+        <is>
+          <t>37-42193 , 37-26944</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="60" customHeight="1" thickBot="1">
+      <c r="A156" s="2" t="n">
+        <v>5336</v>
+      </c>
+      <c r="B156" s="5" t="n">
+        <v>46128</v>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>حمزة القبلاني</t>
+        </is>
+      </c>
+      <c r="E156" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F156" s="7" t="inlineStr">
+        <is>
+          <t>46-11634</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="60" customHeight="1" thickBot="1">
+      <c r="A157" s="2" t="n">
+        <v>5341</v>
+      </c>
+      <c r="B157" s="5" t="n">
+        <v>46130</v>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>عامر ماجد</t>
+        </is>
+      </c>
+      <c r="E157" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F157" s="7" t="inlineStr">
+        <is>
+          <t>42-69517</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="60" customHeight="1" thickBot="1">
+      <c r="A158" s="2" t="n">
+        <v>5344</v>
+      </c>
+      <c r="B158" s="5" t="n">
+        <v>46131</v>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>وليد الافضل</t>
+        </is>
+      </c>
+      <c r="E158" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F158" s="7" t="inlineStr">
+        <is>
+          <t>46-12735</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="60" customHeight="1" thickBot="1">
+      <c r="A159" s="2" t="n">
+        <v>5347</v>
+      </c>
+      <c r="B159" s="5" t="n">
+        <v>46131</v>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>د. طارق عريقات</t>
+        </is>
+      </c>
+      <c r="E159" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="F159" s="7" t="inlineStr">
+        <is>
+          <t>44-36214</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="60" customHeight="1" thickBot="1">
+      <c r="A160" s="2" t="n">
+        <v>5363</v>
+      </c>
+      <c r="B160" s="5" t="n">
+        <v>46132</v>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>هاشم الهنيدي</t>
+        </is>
+      </c>
+      <c r="E160" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F160" s="7" t="inlineStr">
+        <is>
+          <t>46-12916</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="60" customHeight="1" thickBot="1">
+      <c r="A161" s="2" t="n">
+        <v>5384</v>
+      </c>
+      <c r="B161" s="5" t="n">
+        <v>46134</v>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>حسن هزاع</t>
+        </is>
+      </c>
+      <c r="E161" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F161" s="7" t="inlineStr">
+        <is>
+          <t>46-12491</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="60" customHeight="1" thickBot="1">
+      <c r="A162" s="2" t="n">
+        <v>5407</v>
+      </c>
+      <c r="B162" s="5" t="n">
+        <v>46135</v>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>اسامة</t>
+        </is>
+      </c>
+      <c r="E162" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F162" s="7" t="inlineStr">
+        <is>
+          <t>46-11527</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="60" customHeight="1" thickBot="1">
+      <c r="A163" s="2" t="n">
+        <v>5408</v>
+      </c>
+      <c r="B163" s="5" t="n">
+        <v>46135</v>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>محمد نصر الله</t>
+        </is>
+      </c>
+      <c r="E163" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F163" s="7" t="inlineStr">
+        <is>
+          <t>43-82570</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="60" customHeight="1" thickBot="1">
+      <c r="A164" s="2" t="n">
+        <v>5416</v>
+      </c>
+      <c r="B164" s="5" t="n">
+        <v>46137</v>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>محمد الخياط</t>
+        </is>
+      </c>
+      <c r="E164" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F164" s="7" t="inlineStr">
+        <is>
+          <t>44-81798</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="60" customHeight="1" thickBot="1">
+      <c r="A165" s="2" t="n">
+        <v>5417</v>
+      </c>
+      <c r="B165" s="5" t="n">
+        <v>46137</v>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>سخاء الروابدة</t>
+        </is>
+      </c>
+      <c r="E165" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F165" s="7" t="inlineStr">
+        <is>
+          <t>66-67937</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="60" customHeight="1" thickBot="1">
+      <c r="A166" s="2" t="n">
+        <v>5422</v>
+      </c>
+      <c r="B166" s="5" t="n">
+        <v>46138</v>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>احمد الزعبي</t>
+        </is>
+      </c>
+      <c r="E166" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F166" s="7" t="inlineStr">
+        <is>
+          <t>37-66631</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="60" customHeight="1" thickBot="1">
+      <c r="A167" s="2" t="n">
+        <v>5425</v>
+      </c>
+      <c r="B167" s="5" t="n">
+        <v>46138</v>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>محمد الخياط</t>
+        </is>
+      </c>
+      <c r="E167" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F167" s="7" t="inlineStr">
+        <is>
+          <t>44-81798</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="60" customHeight="1" thickBot="1">
+      <c r="A168" s="2" t="n">
+        <v>5426</v>
+      </c>
+      <c r="B168" s="5" t="n">
+        <v>46138</v>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>رسلان</t>
+        </is>
+      </c>
+      <c r="E168" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F168" s="7" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="60" customHeight="1" thickBot="1">
+      <c r="A169" s="2" t="n">
+        <v>5432</v>
+      </c>
+      <c r="B169" s="5" t="n">
+        <v>46139</v>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>اية شموط</t>
+        </is>
+      </c>
+      <c r="E169" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F169" s="7" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="60" customHeight="1" thickBot="1">
+      <c r="A170" s="2" t="n">
+        <v>5438</v>
+      </c>
+      <c r="B170" s="5" t="n">
+        <v>46139</v>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>نادي السيارات الملكي</t>
+        </is>
+      </c>
+      <c r="E170" s="6" t="n">
+        <v>420</v>
+      </c>
+      <c r="F170" s="7" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="60" customHeight="1" thickBot="1">
+      <c r="A171" s="2" t="n">
+        <v>5441</v>
+      </c>
+      <c r="B171" s="5" t="n">
+        <v>46139</v>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>احمد الشعبي</t>
+        </is>
+      </c>
+      <c r="E171" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="F171" s="7" t="inlineStr">
+        <is>
+          <t>46-12879 , 46-3422</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="60" customHeight="1" thickBot="1">
+      <c r="A172" s="2" t="n">
+        <v>5467</v>
+      </c>
+      <c r="B172" s="5" t="n">
+        <v>46141</v>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>الشرباتي</t>
+        </is>
+      </c>
+      <c r="E172" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F172" s="7" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="60" customHeight="1" thickBot="1">
+      <c r="A173" s="2" t="n">
+        <v>5477</v>
+      </c>
+      <c r="B173" s="5" t="n">
+        <v>46141</v>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>احمد الشعبي</t>
+        </is>
+      </c>
+      <c r="E173" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F173" s="7" t="inlineStr">
+        <is>
+          <t>46-13420</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="60" customHeight="1" thickBot="1">
+      <c r="A174" s="2" t="n">
+        <v>5499</v>
+      </c>
+      <c r="B174" s="5" t="n">
+        <v>46142</v>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>احمد الزعبي</t>
+        </is>
+      </c>
+      <c r="E174" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F174" s="7" t="inlineStr">
+        <is>
+          <t>46-12368</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="60" customHeight="1" thickBot="1">
+      <c r="A175" s="2" t="n">
+        <v>5516</v>
+      </c>
+      <c r="B175" s="5" t="n">
+        <v>46144</v>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>عطالله عبد ربه</t>
+        </is>
+      </c>
+      <c r="E175" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F175" s="7" t="inlineStr">
+        <is>
+          <t>46-15174</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="60" customHeight="1" thickBot="1">
+      <c r="A176" s="2" t="n">
+        <v>5520</v>
+      </c>
+      <c r="B176" s="5" t="n">
+        <v>46144</v>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>فيصل العشي</t>
+        </is>
+      </c>
+      <c r="E176" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F176" s="7" t="inlineStr">
+        <is>
+          <t>46-11495</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="60" customHeight="1" thickBot="1">
+      <c r="A177" s="2" t="n">
+        <v>5534</v>
+      </c>
+      <c r="B177" s="5" t="n">
+        <v>46145</v>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>نادي السيارات الملكي</t>
+        </is>
+      </c>
+      <c r="E177" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F177" s="7" t="inlineStr">
+        <is>
+          <t>50-79415</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="60" customHeight="1" thickBot="1">
+      <c r="A178" s="2" t="n">
+        <v>5540</v>
+      </c>
+      <c r="B178" s="5" t="n">
+        <v>46146</v>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>بديع الشامي</t>
+        </is>
+      </c>
+      <c r="E178" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="F178" s="7" t="inlineStr">
+        <is>
+          <t>10-66886 , 10-33302</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="60" customHeight="1" thickBot="1">
+      <c r="A179" s="2" t="n">
+        <v>5546</v>
+      </c>
+      <c r="B179" s="5" t="n">
+        <v>46147</v>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>رائد تادرس</t>
+        </is>
+      </c>
+      <c r="E179" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F179" s="7" t="inlineStr">
+        <is>
+          <t>46-11740</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="60" customHeight="1" thickBot="1">
+      <c r="A180" s="2" t="n">
+        <v>5550</v>
+      </c>
+      <c r="B180" s="5" t="n">
+        <v>46147</v>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>مصطفى فردوس</t>
+        </is>
+      </c>
+      <c r="E180" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F180" s="7" t="inlineStr">
+        <is>
+          <t>48-53131</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="60" customHeight="1" thickBot="1">
+      <c r="A181" s="2" t="n">
+        <v>5552</v>
+      </c>
+      <c r="B181" s="5" t="n">
+        <v>46147</v>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>نوير النبر</t>
+        </is>
+      </c>
+      <c r="E181" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="F181" s="7" t="inlineStr">
+        <is>
+          <t>37-78844 , 46-8283</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="60" customHeight="1" thickBot="1">
+      <c r="A182" s="2" t="n">
+        <v>5558</v>
+      </c>
+      <c r="B182" s="5" t="n">
+        <v>46148</v>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>اشرف دحدل</t>
+        </is>
+      </c>
+      <c r="E182" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F182" s="7" t="inlineStr">
+        <is>
+          <t>46-13861</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="60" customHeight="1" thickBot="1">
+      <c r="A183" s="2" t="n">
+        <v>5561</v>
+      </c>
+      <c r="B183" s="5" t="n">
+        <v>46148</v>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>محمد احمد</t>
+        </is>
+      </c>
+      <c r="E183" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F183" s="7" t="inlineStr">
+        <is>
+          <t>46-10248</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="60" customHeight="1" thickBot="1">
+      <c r="A184" s="2" t="n">
+        <v>5568</v>
+      </c>
+      <c r="B184" s="5" t="n">
+        <v>46148</v>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>حسن تحبسم</t>
+        </is>
+      </c>
+      <c r="E184" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F184" s="7" t="inlineStr">
+        <is>
+          <t>37-80190 , 46-6211</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="60" customHeight="1" thickBot="1">
+      <c r="A185" s="2" t="n">
+        <v>5578</v>
+      </c>
+      <c r="B185" s="5" t="n">
+        <v>46149</v>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>الشريف تاج الدين</t>
+        </is>
+      </c>
+      <c r="E185" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F185" s="7" t="inlineStr">
+        <is>
+          <t>46-13485</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="60" customHeight="1" thickBot="1">
+      <c r="A186" s="2" t="n">
+        <v>5591</v>
+      </c>
+      <c r="B186" s="5" t="n">
+        <v>46151</v>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>احمد ابو الرب</t>
+        </is>
+      </c>
+      <c r="E186" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F186" s="7" t="inlineStr">
+        <is>
+          <t>46-61752</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="60" customHeight="1" thickBot="1">
+      <c r="A187" s="2" t="n">
+        <v>5593</v>
+      </c>
+      <c r="B187" s="5" t="n">
+        <v>46151</v>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>مصطفى فردوس</t>
+        </is>
+      </c>
+      <c r="E187" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F187" s="7" t="inlineStr">
+        <is>
+          <t>48-53131</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="60" customHeight="1" thickBot="1">
+      <c r="A188" s="2" t="n">
+        <v>5597</v>
+      </c>
+      <c r="B188" s="5" t="n">
+        <v>46151</v>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>ركان</t>
+        </is>
+      </c>
+      <c r="E188" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F188" s="7" t="inlineStr">
+        <is>
+          <t>46-13460</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="60" customHeight="1" thickBot="1">
+      <c r="A189" s="2" t="n">
+        <v>5605</v>
+      </c>
+      <c r="B189" s="5" t="n">
+        <v>46151</v>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>ركان</t>
+        </is>
+      </c>
+      <c r="E189" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F189" s="7" t="inlineStr">
+        <is>
+          <t>46-13460</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="60" customHeight="1" thickBot="1">
+      <c r="A190" s="2" t="n">
+        <v>5610</v>
+      </c>
+      <c r="B190" s="5" t="n">
+        <v>46152</v>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>نادي السيارات الملكي</t>
+        </is>
+      </c>
+      <c r="E190" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F190" s="7" t="inlineStr">
+        <is>
+          <t>0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="60" customHeight="1" thickBot="1">
+      <c r="A191" s="2" t="n">
+        <v>5631</v>
+      </c>
+      <c r="B191" s="5" t="n">
+        <v>46153</v>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>عاصم عصام</t>
+        </is>
+      </c>
+      <c r="E191" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F191" s="7" t="inlineStr">
+        <is>
+          <t>46-12583</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="60" customHeight="1" thickBot="1">
+      <c r="A192" s="2" t="n">
+        <v>5639</v>
+      </c>
+      <c r="B192" s="5" t="n">
+        <v>46153</v>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>نادي السيارات الملكي</t>
+        </is>
+      </c>
+      <c r="E192" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F192" s="7" t="inlineStr">
+        <is>
+          <t>0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="60" customHeight="1" thickBot="1">
+      <c r="A193" s="2" t="n">
+        <v>5654</v>
+      </c>
+      <c r="B193" s="5" t="n">
+        <v>46154</v>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>شعلان</t>
+        </is>
+      </c>
+      <c r="E193" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F193" s="7" t="inlineStr">
+        <is>
+          <t>46-14840</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="60" customHeight="1" thickBot="1">
+      <c r="A194" s="2" t="n">
+        <v>5679</v>
+      </c>
+      <c r="B194" s="5" t="n">
+        <v>46155</v>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>بديع الشامي</t>
+        </is>
+      </c>
+      <c r="E194" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F194" s="7" t="inlineStr">
+        <is>
+          <t>10-66886</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="60" customHeight="1" thickBot="1">
+      <c r="A195" s="2" t="n">
+        <v>5700</v>
+      </c>
+      <c r="B195" s="5" t="n">
+        <v>46156</v>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>علاء مصطفى</t>
+        </is>
+      </c>
+      <c r="E195" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F195" s="7" t="inlineStr">
+        <is>
+          <t>66-18324</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="60" customHeight="1" thickBot="1">
+      <c r="A196" s="2" t="n">
+        <v>5714</v>
+      </c>
+      <c r="B196" s="5" t="n">
+        <v>46158</v>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>علاء عربيات</t>
+        </is>
+      </c>
+      <c r="E196" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="F196" s="7" t="inlineStr">
+        <is>
+          <t>36-95061 , na</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="60" customHeight="1" thickBot="1">
+      <c r="A197" s="2" t="n">
+        <v>5718</v>
+      </c>
+      <c r="B197" s="5" t="n">
+        <v>46159</v>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>يحيى النعيمات</t>
+        </is>
+      </c>
+      <c r="E197" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F197" s="7" t="inlineStr">
+        <is>
+          <t>45-65369</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="60" customHeight="1" thickBot="1">
+      <c r="A198" s="2" t="n">
+        <v>5719</v>
+      </c>
+      <c r="B198" s="5" t="n">
+        <v>46159</v>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>عبود صالح</t>
+        </is>
+      </c>
+      <c r="E198" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F198" s="7" t="inlineStr">
+        <is>
+          <t>46-12349</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="60" customHeight="1" thickBot="1">
+      <c r="A199" s="2" t="n">
+        <v>5739</v>
+      </c>
+      <c r="B199" s="5" t="n">
+        <v>46160</v>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>عادل شابسوغ</t>
+        </is>
+      </c>
+      <c r="E199" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F199" s="7" t="inlineStr">
+        <is>
+          <t>48-11079</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="60" customHeight="1" thickBot="1">
+      <c r="A200" s="2" t="n">
+        <v>5751</v>
+      </c>
+      <c r="B200" s="5" t="n">
+        <v>46160</v>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>مهند جعبة</t>
+        </is>
+      </c>
+      <c r="E200" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F200" s="7" t="inlineStr">
+        <is>
+          <t>36-95061</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="60" customHeight="1" thickBot="1">
+      <c r="A201" s="2" t="n">
+        <v>5752</v>
+      </c>
+      <c r="B201" s="5" t="n">
+        <v>46161</v>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>ناصر الفاعوري</t>
+        </is>
+      </c>
+      <c r="E201" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F201" s="7" t="inlineStr">
+        <is>
+          <t>44-34717</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="60" customHeight="1" thickBot="1">
+      <c r="A202" s="2" t="n">
+        <v>5762</v>
+      </c>
+      <c r="B202" s="5" t="n">
+        <v>46161</v>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>مأمون زهران</t>
+        </is>
+      </c>
+      <c r="E202" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F202" s="7" t="inlineStr">
+        <is>
+          <t>1-10772</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="60" customHeight="1" thickBot="1">
+      <c r="A203" s="2" t="n">
+        <v>5774</v>
+      </c>
+      <c r="B203" s="5" t="n">
+        <v>46162</v>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>فيصل الفايز</t>
+        </is>
+      </c>
+      <c r="E203" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="F203" s="7" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="60" customHeight="1" thickBot="1">
+      <c r="A204" s="2" t="n">
+        <v>5778</v>
+      </c>
+      <c r="B204" s="5" t="n">
+        <v>46162</v>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>غازي ابو الراغب</t>
+        </is>
+      </c>
+      <c r="E204" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F204" s="7" t="inlineStr">
+        <is>
+          <t>46-54583 , 44-52282</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="60" customHeight="1" thickBot="1">
+      <c r="A205" s="2" t="n">
+        <v>5792</v>
+      </c>
+      <c r="B205" s="5" t="n">
+        <v>46163</v>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>فيصل الفايز</t>
+        </is>
+      </c>
+      <c r="E205" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F205" s="7" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="60" customHeight="1" thickBot="1">
+      <c r="A206" s="2" t="n">
+        <v>5805</v>
+      </c>
+      <c r="B206" s="5" t="n">
+        <v>46165</v>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>اسحق القواسمي</t>
+        </is>
+      </c>
+      <c r="E206" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F206" s="7" t="inlineStr">
+        <is>
+          <t>14-28940</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="60" customHeight="1" thickBot="1">
+      <c r="A207" s="2" t="n">
+        <v>5808</v>
+      </c>
+      <c r="B207" s="5" t="n">
+        <v>46165</v>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>زياد القرم</t>
+        </is>
+      </c>
+      <c r="E207" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F207" s="7" t="inlineStr">
+        <is>
+          <t>46-11688 , 37-83828 , na</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="60" customHeight="1" thickBot="1">
+      <c r="A208" s="2" t="n">
+        <v>5814</v>
+      </c>
+      <c r="B208" s="5" t="n">
+        <v>46165</v>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>شركة مارغاريتا  لصناعة وتجارة الدراجات</t>
+        </is>
+      </c>
+      <c r="E208" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="F208" s="7" t="inlineStr">
+        <is>
+          <t>00637 , 088 , 562 , 871</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="60" customHeight="1" thickBot="1">
+      <c r="A209" s="2" t="n">
+        <v>5828</v>
+      </c>
+      <c r="B209" s="5" t="n">
+        <v>46166</v>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>شركة بيسان لتجارة الدراجات</t>
+        </is>
+      </c>
+      <c r="E209" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F209" s="7" t="inlineStr">
+        <is>
+          <t>55 , 66</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="60" customHeight="1" thickBot="1">
+      <c r="A210" s="2" t="n">
+        <v>5834</v>
+      </c>
+      <c r="B210" s="5" t="n">
+        <v>46166</v>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>محمود نصار</t>
+        </is>
+      </c>
+      <c r="E210" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F210" s="7" t="inlineStr">
+        <is>
+          <t>42-79228</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="60" customHeight="1" thickBot="1">
+      <c r="A211" s="2" t="n">
+        <v>5835</v>
+      </c>
+      <c r="B211" s="5" t="n">
+        <v>46173</v>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>د. جميل القطاني</t>
+        </is>
+      </c>
+      <c r="E211" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F211" s="7" t="inlineStr">
+        <is>
+          <t>45-20632</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="60" customHeight="1" thickBot="1">
+      <c r="A212" s="2" t="n">
+        <v>5838</v>
+      </c>
+      <c r="B212" s="5" t="n">
+        <v>46173</v>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>منذر محمد</t>
+        </is>
+      </c>
+      <c r="E212" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F212" s="7" t="inlineStr">
+        <is>
+          <t>٢١٧ ksa</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="60" customHeight="1" thickBot="1">
+      <c r="A213" s="2" t="n">
+        <v>5843</v>
+      </c>
+      <c r="B213" s="5" t="n">
+        <v>46173</v>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>معن ابو صفية</t>
+        </is>
+      </c>
+      <c r="E213" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F213" s="7" t="inlineStr">
+        <is>
+          <t>37-89086</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="60" customHeight="1" thickBot="1">
+      <c r="A214" s="2" t="n">
+        <v>5848</v>
+      </c>
+      <c r="B214" s="5" t="n">
+        <v>46173</v>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>ابو وديع</t>
+        </is>
+      </c>
+      <c r="E214" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F214" s="7" t="inlineStr">
+        <is>
+          <t>37-79872</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="60" customHeight="1" thickBot="1">
+      <c r="A215" s="2" t="n">
+        <v>5854</v>
+      </c>
+      <c r="B215" s="5" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>مهاب بسطامي</t>
+        </is>
+      </c>
+      <c r="E215" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F215" s="7" t="inlineStr">
+        <is>
+          <t>41-1440</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="60" customHeight="1" thickBot="1">
+      <c r="A216" s="2" t="n">
+        <v>5856</v>
+      </c>
+      <c r="B216" s="5" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>غازي ابو الراغب</t>
+        </is>
+      </c>
+      <c r="E216" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F216" s="7" t="inlineStr">
+        <is>
+          <t>44-52282 , na</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="60" customHeight="1" thickBot="1">
+      <c r="A217" s="2" t="n">
+        <v>5864</v>
+      </c>
+      <c r="B217" s="5" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>خالد الهواري</t>
+        </is>
+      </c>
+      <c r="E217" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F217" s="7" t="inlineStr">
+        <is>
+          <t>47-83440</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="60" customHeight="1" thickBot="1">
+      <c r="A218" s="2" t="n">
+        <v>5880</v>
+      </c>
+      <c r="B218" s="5" t="n">
+        <v>46176</v>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>وائل صفوري</t>
+        </is>
+      </c>
+      <c r="E218" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F218" s="7" t="inlineStr">
+        <is>
+          <t>46-14156</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="60" customHeight="1" thickBot="1">
+      <c r="A219" s="2" t="n">
+        <v>5881</v>
+      </c>
+      <c r="B219" s="5" t="n">
+        <v>46176</v>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>ادمون الاشهب</t>
+        </is>
+      </c>
+      <c r="E219" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F219" s="7" t="inlineStr">
+        <is>
+          <t>49-13395</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="60" customHeight="1" thickBot="1">
+      <c r="A220" s="2" t="n">
+        <v>5888</v>
+      </c>
+      <c r="B220" s="5" t="n">
+        <v>46176</v>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>علاء القطاونة</t>
+        </is>
+      </c>
+      <c r="E220" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F220" s="7" t="inlineStr">
+        <is>
+          <t>16-36172</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="60" customHeight="1" thickBot="1">
+      <c r="A221" s="2" t="n">
+        <v>5892</v>
+      </c>
+      <c r="B221" s="5" t="n">
+        <v>46177</v>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>عزت عودة</t>
+        </is>
+      </c>
+      <c r="E221" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="F221" s="7" t="inlineStr">
+        <is>
+          <t>80-9767 , 88-9767</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="60" customHeight="1" thickBot="1">
+      <c r="A222" s="2" t="n">
+        <v>5901</v>
+      </c>
+      <c r="B222" s="5" t="n">
+        <v>46179</v>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>فؤاد ابو ركب</t>
+        </is>
+      </c>
+      <c r="E222" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F222" s="7" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="60" customHeight="1" thickBot="1">
+      <c r="A223" s="2" t="n">
+        <v>5902</v>
+      </c>
+      <c r="B223" s="5" t="n">
+        <v>46179</v>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>محمد رماحة</t>
+        </is>
+      </c>
+      <c r="E223" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="F223" s="7" t="inlineStr">
+        <is>
+          <t>46-11838</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="60" customHeight="1" thickBot="1">
+      <c r="A224" s="2" t="n">
+        <v>5905</v>
+      </c>
+      <c r="B224" s="5" t="n">
+        <v>46179</v>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>ابو ماجد</t>
+        </is>
+      </c>
+      <c r="E224" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="F224" s="7" t="inlineStr">
+        <is>
+          <t>43-94972 , 66-46563</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="60" customHeight="1" thickBot="1">
+      <c r="A225" s="2" t="n">
+        <v>5925</v>
+      </c>
+      <c r="B225" s="5" t="n">
+        <v>46180</v>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>نادي السيارات الملكي</t>
+        </is>
+      </c>
+      <c r="E225" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F225" s="7" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="60" customHeight="1" thickBot="1">
+      <c r="A226" s="2" t="n">
+        <v>5926</v>
+      </c>
+      <c r="B226" s="5" t="n">
+        <v>46180</v>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>نادي السيارات الملكي</t>
+        </is>
+      </c>
+      <c r="E226" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="F226" s="7" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="60" customHeight="1" thickBot="1">
+      <c r="A227" s="2" t="n">
+        <v>5928</v>
+      </c>
+      <c r="B227" s="5" t="n">
+        <v>46180</v>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>نادي السيارات الملكي</t>
+        </is>
+      </c>
+      <c r="E227" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F227" s="7" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="60" customHeight="1" thickBot="1">
+      <c r="A228" s="2" t="n">
+        <v>5942</v>
+      </c>
+      <c r="B228" s="5" t="n">
+        <v>46181</v>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>نقدي</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>علي طه</t>
+        </is>
+      </c>
+      <c r="E228" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F228" s="7" t="inlineStr">
+        <is>
+          <t>37-79729</t>
+        </is>
+      </c>
     </row>
     <row r="229" hidden="1" ht="60" customHeight="1" thickBot="1">
       <c r="A229" s="2" t="n"/>
@@ -40736,7 +44768,7 @@
         </is>
       </c>
       <c r="D5003" s="6" t="n">
-        <v>1060</v>
+        <v>9585.01</v>
       </c>
       <c r="E5003" s="20" t="n"/>
     </row>
